--- a/006_DASSAULT_AETHER/gridConvergence_D01_V1.xlsx
+++ b/006_DASSAULT_AETHER/gridConvergence_D01_V1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\DA\SOC\NP\ORG\DGT\UNIX\SCIENTIFIQUE\CSC\PROJET\GIVRE\IPW3\006_DASSAULT_AETHER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mkzayni/Desktop/UNIVERSITY/POST_PROCESS/postProcessingData/006_DASSAULT_AETHER/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D919AF0A-BA65-45A4-8D86-F3380B61E778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6553F997-FC29-D341-A3B6-65275F298E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26720" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INSTRUCTIONS" sheetId="1" r:id="rId1"/>
@@ -37,9 +37,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -452,7 +449,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -820,16 +817,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -844,13 +842,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -862,7 +854,13 @@
     <xf numFmtId="165" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -874,12 +872,6 @@
     <xf numFmtId="165" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -889,10 +881,15 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -979,7 +976,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1296,386 +1293,386 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E78"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="17.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="96.3046875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.765625" customWidth="1"/>
-    <col min="5" max="5" width="16.3046875" customWidth="1"/>
-    <col min="6" max="6" width="17.4609375" customWidth="1"/>
-    <col min="7" max="7" width="14.4609375" customWidth="1"/>
+    <col min="1" max="1" width="96.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="17.5" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.5">
-      <c r="A1" s="48" t="s">
+    <row r="1" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15.5">
-      <c r="A2" s="48"/>
-    </row>
-    <row r="3" spans="1:1" ht="15.5">
-      <c r="A3" s="48"/>
-    </row>
-    <row r="4" spans="1:1" ht="15.5">
-      <c r="A4" s="48" t="s">
+    <row r="2" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="51"/>
+    </row>
+    <row r="3" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="51"/>
+    </row>
+    <row r="4" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="51" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.5">
-      <c r="A5" s="48"/>
-    </row>
-    <row r="6" spans="1:1" ht="20">
+    <row r="5" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="51"/>
+    </row>
+    <row r="6" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="20">
+    <row r="7" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="20">
+    <row r="8" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="20">
+    <row r="9" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="20">
+    <row r="10" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="20">
+    <row r="11" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="20">
+    <row r="12" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="15.5">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="52" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="15.5">
-      <c r="A14" s="49"/>
-    </row>
-    <row r="15" spans="1:1" ht="20">
+    <row r="14" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="52"/>
+    </row>
+    <row r="15" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="20">
+    <row r="16" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="20">
+    <row r="17" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="20">
+    <row r="18" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="20">
+    <row r="19" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.5">
-      <c r="A20" s="48" t="s">
+    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="51" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.5">
-      <c r="A21" s="48"/>
-    </row>
-    <row r="22" spans="1:5" ht="20">
+    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="51"/>
+    </row>
+    <row r="22" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="20">
+    <row r="23" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="20">
+    <row r="24" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="20">
+    <row r="25" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="20">
+    <row r="26" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="20">
+    <row r="27" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E27" s="4"/>
     </row>
-    <row r="28" spans="1:5" ht="20">
+    <row r="28" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="20">
+    <row r="29" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="20">
+    <row r="30" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E30" s="4"/>
     </row>
-    <row r="31" spans="1:5" ht="20">
+    <row r="31" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E31" s="4"/>
     </row>
-    <row r="32" spans="1:5" ht="15.5">
-      <c r="A32" s="48" t="s">
+    <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="51" t="s">
         <v>22</v>
       </c>
       <c r="E32" s="4"/>
     </row>
-    <row r="33" spans="1:5" ht="15.5">
-      <c r="A33" s="48"/>
+    <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="51"/>
       <c r="E33" s="4"/>
     </row>
-    <row r="34" spans="1:5" ht="20">
+    <row r="34" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E34" s="4"/>
     </row>
-    <row r="35" spans="1:5" ht="20">
+    <row r="35" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="4"/>
     </row>
-    <row r="36" spans="1:5" ht="20">
+    <row r="36" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E36" s="4"/>
     </row>
-    <row r="37" spans="1:5" ht="20">
+    <row r="37" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E37" s="4"/>
     </row>
-    <row r="38" spans="1:5" ht="20">
+    <row r="38" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>24</v>
       </c>
       <c r="E38" s="4"/>
     </row>
-    <row r="39" spans="1:5" ht="20">
+    <row r="39" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="20">
+    <row r="40" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E40" s="4"/>
     </row>
-    <row r="41" spans="1:5" ht="20">
+    <row r="41" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E41" s="4"/>
     </row>
-    <row r="42" spans="1:5" ht="20">
+    <row r="42" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E42" s="4"/>
     </row>
-    <row r="43" spans="1:5" ht="20">
+    <row r="43" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:5" ht="15.5">
-      <c r="A44" s="48" t="s">
+    <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A44" s="51" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15.5">
-      <c r="A45" s="48"/>
+    <row r="45" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A45" s="51"/>
       <c r="E45" s="4"/>
     </row>
-    <row r="46" spans="1:5" ht="20">
+    <row r="46" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E46" s="4"/>
     </row>
-    <row r="47" spans="1:5" ht="20">
+    <row r="47" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E47" s="4"/>
     </row>
-    <row r="48" spans="1:5" ht="20">
+    <row r="48" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E48" s="4"/>
     </row>
-    <row r="49" spans="1:5" ht="20">
+    <row r="49" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>29</v>
       </c>
       <c r="E49" s="4"/>
     </row>
-    <row r="50" spans="1:5" ht="20">
+    <row r="50" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E50" s="4"/>
     </row>
-    <row r="51" spans="1:5" ht="20">
+    <row r="51" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="E51" s="4"/>
     </row>
-    <row r="52" spans="1:5" ht="20">
+    <row r="52" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E52" s="4"/>
     </row>
-    <row r="53" spans="1:5" ht="20">
+    <row r="53" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>33</v>
       </c>
       <c r="E53" s="4"/>
     </row>
-    <row r="54" spans="1:5" ht="20">
+    <row r="54" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E54" s="4"/>
     </row>
-    <row r="55" spans="1:5" ht="20">
+    <row r="55" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E55" s="4"/>
     </row>
-    <row r="56" spans="1:5" ht="15.5">
-      <c r="A56" s="48" t="s">
+    <row r="56" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A56" s="51" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.5">
-      <c r="A57" s="48"/>
+    <row r="57" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A57" s="51"/>
       <c r="E57" s="4"/>
     </row>
-    <row r="58" spans="1:5" ht="20">
+    <row r="58" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>36</v>
       </c>
       <c r="E58" s="4"/>
     </row>
-    <row r="59" spans="1:5" ht="20">
+    <row r="59" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
         <v>37</v>
       </c>
       <c r="E59" s="4"/>
     </row>
-    <row r="60" spans="1:5" ht="20">
+    <row r="60" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
         <v>68</v>
       </c>
       <c r="E60" s="4"/>
     </row>
-    <row r="61" spans="1:5" ht="20">
+    <row r="61" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E61" s="4"/>
     </row>
-    <row r="62" spans="1:5" ht="20">
+    <row r="62" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E62" s="4"/>
     </row>
-    <row r="63" spans="1:5" ht="20">
+    <row r="63" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E63" s="4"/>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E64" s="4"/>
     </row>
-    <row r="65" spans="5:5">
+    <row r="65" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E65" s="4"/>
     </row>
-    <row r="66" spans="5:5">
+    <row r="66" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E66" s="4"/>
     </row>
-    <row r="68" spans="5:5">
+    <row r="68" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E68" s="4"/>
     </row>
-    <row r="69" spans="5:5">
+    <row r="69" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E69" s="4"/>
     </row>
-    <row r="70" spans="5:5">
+    <row r="70" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E70" s="4"/>
     </row>
-    <row r="71" spans="5:5">
+    <row r="71" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E71" s="4"/>
     </row>
-    <row r="72" spans="5:5">
+    <row r="72" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E72" s="4"/>
     </row>
-    <row r="73" spans="5:5">
+    <row r="73" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E73" s="4"/>
     </row>
-    <row r="74" spans="5:5">
+    <row r="74" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E74" s="4"/>
     </row>
-    <row r="75" spans="5:5">
+    <row r="75" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E75" s="4"/>
     </row>
-    <row r="76" spans="5:5">
+    <row r="76" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E76" s="4"/>
     </row>
-    <row r="77" spans="5:5">
+    <row r="77" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E77" s="4"/>
     </row>
-    <row r="78" spans="5:5">
+    <row r="78" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E78" s="4"/>
     </row>
   </sheetData>
@@ -1696,36 +1693,36 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AMG78"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.765625" defaultRowHeight="15.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.07421875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.4609375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.07421875" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.4609375" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.07421875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24" style="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="31.4609375" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.07421875" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24" style="10" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="18" width="13.69140625" style="10" customWidth="1"/>
-    <col min="19" max="1021" width="10.765625" style="10"/>
+    <col min="13" max="18" width="13.6640625" style="10" customWidth="1"/>
+    <col min="19" max="1021" width="10.83203125" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1021" s="32" customFormat="1" ht="25">
-      <c r="D1" s="52" t="s">
+    <row r="1" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
+      <c r="D1" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
       <c r="M1" s="31"/>
       <c r="N1" s="31"/>
       <c r="O1" s="31"/>
@@ -2736,37 +2733,37 @@
       <c r="AMF1" s="31"/>
       <c r="AMG1" s="31"/>
     </row>
-    <row r="2" spans="1:1021" s="6" customFormat="1" ht="59.15" customHeight="1">
-      <c r="A2" s="68" t="s">
+    <row r="2" spans="1:1021" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="70"/>
-    </row>
-    <row r="3" spans="1:1021" s="32" customFormat="1" ht="25">
-      <c r="A3" s="63" t="s">
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="69"/>
+    </row>
+    <row r="3" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
+      <c r="A3" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="65"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="66"/>
       <c r="M3" s="31"/>
       <c r="N3" s="31"/>
       <c r="O3" s="31"/>
@@ -3777,27 +3774,27 @@
       <c r="AMF3" s="31"/>
       <c r="AMG3" s="31"/>
     </row>
-    <row r="4" spans="1:1021" s="32" customFormat="1" ht="25">
-      <c r="A4" s="59" t="s">
+    <row r="4" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
+      <c r="A4" s="58" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="62" t="s">
+      <c r="B4" s="59"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62" t="s">
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62" t="s">
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="62"/>
-      <c r="L4" s="62"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
       <c r="M4" s="31"/>
       <c r="N4" s="31"/>
       <c r="O4" s="21"/>
@@ -4808,7 +4805,7 @@
       <c r="AMF4" s="31"/>
       <c r="AMG4" s="31"/>
     </row>
-    <row r="5" spans="1:1021">
+    <row r="5" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="A5" s="35" t="s">
         <v>50</v>
       </c>
@@ -4846,7 +4843,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:1021">
+    <row r="6" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="A6" s="35">
         <v>1</v>
       </c>
@@ -4876,7 +4873,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="7" spans="1:1021">
+    <row r="7" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="D7" s="30">
         <v>2</v>
       </c>
@@ -4899,7 +4896,7 @@
         <v>10.039999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:1021">
+    <row r="8" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="D8" s="30">
         <v>3</v>
       </c>
@@ -4922,7 +4919,7 @@
         <v>11.94</v>
       </c>
     </row>
-    <row r="9" spans="1:1021">
+    <row r="9" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="D9" s="19"/>
       <c r="E9" s="11"/>
       <c r="F9" s="19"/>
@@ -4941,7 +4938,7 @@
         <v>13.56</v>
       </c>
     </row>
-    <row r="10" spans="1:1021">
+    <row r="10" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="G10" s="30">
         <v>5</v>
       </c>
@@ -4957,7 +4954,7 @@
         <v>15.22</v>
       </c>
     </row>
-    <row r="11" spans="1:1021">
+    <row r="11" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="G11" s="30">
         <v>6</v>
       </c>
@@ -4973,7 +4970,7 @@
         <v>16.82</v>
       </c>
     </row>
-    <row r="12" spans="1:1021">
+    <row r="12" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="G12" s="30">
         <v>7</v>
       </c>
@@ -4989,7 +4986,7 @@
         <v>18.239999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:1021">
+    <row r="13" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="G13" s="19"/>
       <c r="H13" s="42"/>
       <c r="I13" s="19"/>
@@ -5001,7 +4998,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:1021">
+    <row r="14" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J14" s="30">
         <v>9</v>
       </c>
@@ -5010,7 +5007,7 @@
         <v>21.58</v>
       </c>
     </row>
-    <row r="15" spans="1:1021">
+    <row r="15" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J15" s="30">
         <v>10</v>
       </c>
@@ -5019,7 +5016,7 @@
         <v>23.18</v>
       </c>
     </row>
-    <row r="16" spans="1:1021">
+    <row r="16" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J16" s="30">
         <v>11</v>
       </c>
@@ -5028,7 +5025,7 @@
         <v>24.78</v>
       </c>
     </row>
-    <row r="17" spans="1:1021">
+    <row r="17" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J17" s="30">
         <v>12</v>
       </c>
@@ -5037,7 +5034,7 @@
         <v>26.44</v>
       </c>
     </row>
-    <row r="18" spans="1:1021">
+    <row r="18" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J18" s="30">
         <v>13</v>
       </c>
@@ -5046,7 +5043,7 @@
         <v>28.06</v>
       </c>
     </row>
-    <row r="19" spans="1:1021">
+    <row r="19" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J19" s="30">
         <v>14</v>
       </c>
@@ -5055,7 +5052,7 @@
         <v>29.96</v>
       </c>
     </row>
-    <row r="20" spans="1:1021">
+    <row r="20" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J20" s="30">
         <v>15</v>
       </c>
@@ -5064,28 +5061,28 @@
         <v>32.42</v>
       </c>
     </row>
-    <row r="21" spans="1:1021">
+    <row r="21" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J21" s="24"/>
       <c r="K21" s="44"/>
       <c r="L21" s="24"/>
       <c r="M21" s="15"/>
       <c r="N21" s="15"/>
     </row>
-    <row r="22" spans="1:1021" s="32" customFormat="1" ht="25">
-      <c r="A22" s="62" t="s">
+    <row r="22" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
+      <c r="A22" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="62"/>
-      <c r="L22" s="62"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="57"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="57"/>
       <c r="M22" s="33"/>
       <c r="N22" s="33"/>
       <c r="O22" s="31"/>
@@ -6096,27 +6093,27 @@
       <c r="AMF22" s="31"/>
       <c r="AMG22" s="31"/>
     </row>
-    <row r="23" spans="1:1021" s="32" customFormat="1" ht="25">
-      <c r="A23" s="59" t="s">
+    <row r="23" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
+      <c r="A23" s="58" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="60"/>
-      <c r="C23" s="61"/>
-      <c r="D23" s="62" t="s">
+      <c r="B23" s="59"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62" t="s">
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62" t="s">
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="K23" s="62"/>
-      <c r="L23" s="62"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
       <c r="M23" s="31"/>
       <c r="N23" s="31"/>
       <c r="O23" s="31"/>
@@ -7127,7 +7124,7 @@
       <c r="AMF23" s="31"/>
       <c r="AMG23" s="31"/>
     </row>
-    <row r="24" spans="1:1021">
+    <row r="24" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="A24" s="35" t="s">
         <v>50</v>
       </c>
@@ -7165,7 +7162,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:1021">
+    <row r="25" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="A25" s="35">
         <v>1</v>
       </c>
@@ -7195,7 +7192,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="26" spans="1:1021">
+    <row r="26" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="D26" s="30">
         <v>2</v>
       </c>
@@ -7218,7 +7215,7 @@
         <v>10.039999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:1021">
+    <row r="27" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="D27" s="30">
         <v>3</v>
       </c>
@@ -7241,7 +7238,7 @@
         <v>11.94</v>
       </c>
     </row>
-    <row r="28" spans="1:1021">
+    <row r="28" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="D28" s="19"/>
       <c r="E28" s="11"/>
       <c r="F28" s="19"/>
@@ -7260,7 +7257,7 @@
         <v>13.56</v>
       </c>
     </row>
-    <row r="29" spans="1:1021">
+    <row r="29" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="G29" s="30">
         <v>5</v>
       </c>
@@ -7276,7 +7273,7 @@
         <v>15.22</v>
       </c>
     </row>
-    <row r="30" spans="1:1021">
+    <row r="30" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="G30" s="30">
         <v>6</v>
       </c>
@@ -7292,7 +7289,7 @@
         <v>16.82</v>
       </c>
     </row>
-    <row r="31" spans="1:1021">
+    <row r="31" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="G31" s="30">
         <v>7</v>
       </c>
@@ -7308,7 +7305,7 @@
         <v>18.239999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:1021">
+    <row r="32" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="G32" s="19"/>
       <c r="H32" s="42"/>
       <c r="I32" s="19"/>
@@ -7320,7 +7317,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:1021">
+    <row r="33" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J33" s="30">
         <v>9</v>
       </c>
@@ -7329,7 +7326,7 @@
         <v>21.58</v>
       </c>
     </row>
-    <row r="34" spans="1:1021">
+    <row r="34" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J34" s="30">
         <v>10</v>
       </c>
@@ -7338,7 +7335,7 @@
         <v>23.18</v>
       </c>
     </row>
-    <row r="35" spans="1:1021">
+    <row r="35" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J35" s="30">
         <v>11</v>
       </c>
@@ -7347,7 +7344,7 @@
         <v>24.78</v>
       </c>
     </row>
-    <row r="36" spans="1:1021">
+    <row r="36" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J36" s="30">
         <v>12</v>
       </c>
@@ -7356,7 +7353,7 @@
         <v>26.44</v>
       </c>
     </row>
-    <row r="37" spans="1:1021">
+    <row r="37" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J37" s="30">
         <v>13</v>
       </c>
@@ -7365,7 +7362,7 @@
         <v>28.06</v>
       </c>
     </row>
-    <row r="38" spans="1:1021">
+    <row r="38" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J38" s="30">
         <v>14</v>
       </c>
@@ -7374,7 +7371,7 @@
         <v>29.96</v>
       </c>
     </row>
-    <row r="39" spans="1:1021">
+    <row r="39" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J39" s="30">
         <v>15</v>
       </c>
@@ -7383,26 +7380,26 @@
         <v>32.42</v>
       </c>
     </row>
-    <row r="40" spans="1:1021">
+    <row r="40" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J40" s="24"/>
       <c r="K40" s="44"/>
       <c r="L40" s="24"/>
     </row>
-    <row r="41" spans="1:1021" s="32" customFormat="1" ht="25">
-      <c r="A41" s="67" t="s">
+    <row r="41" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
+      <c r="A41" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="B41" s="67"/>
-      <c r="C41" s="67"/>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
-      <c r="H41" s="67"/>
-      <c r="I41" s="67"/>
-      <c r="J41" s="67"/>
-      <c r="K41" s="67"/>
-      <c r="L41" s="67"/>
+      <c r="B41" s="70"/>
+      <c r="C41" s="70"/>
+      <c r="D41" s="70"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="70"/>
+      <c r="H41" s="70"/>
+      <c r="I41" s="70"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="70"/>
       <c r="M41" s="31"/>
       <c r="N41" s="31"/>
       <c r="O41" s="31"/>
@@ -8413,27 +8410,27 @@
       <c r="AMF41" s="31"/>
       <c r="AMG41" s="31"/>
     </row>
-    <row r="42" spans="1:1021" s="32" customFormat="1" ht="25">
-      <c r="A42" s="59" t="s">
+    <row r="42" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
+      <c r="A42" s="58" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="60"/>
-      <c r="C42" s="61"/>
-      <c r="D42" s="62" t="s">
+      <c r="B42" s="59"/>
+      <c r="C42" s="60"/>
+      <c r="D42" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="62"/>
-      <c r="F42" s="62"/>
-      <c r="G42" s="62" t="s">
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H42" s="62"/>
-      <c r="I42" s="62"/>
-      <c r="J42" s="62" t="s">
+      <c r="H42" s="57"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="K42" s="62"/>
-      <c r="L42" s="62"/>
+      <c r="K42" s="57"/>
+      <c r="L42" s="57"/>
       <c r="M42" s="31"/>
       <c r="N42" s="31"/>
       <c r="O42" s="31"/>
@@ -9444,7 +9441,7 @@
       <c r="AMF42" s="31"/>
       <c r="AMG42" s="31"/>
     </row>
-    <row r="43" spans="1:1021">
+    <row r="43" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="A43" s="35" t="s">
         <v>50</v>
       </c>
@@ -9482,7 +9479,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:1021">
+    <row r="44" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="A44" s="35">
         <v>1</v>
       </c>
@@ -9512,7 +9509,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="45" spans="1:1021">
+    <row r="45" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="D45" s="30">
         <v>2</v>
       </c>
@@ -9535,7 +9532,7 @@
         <v>10.039999999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:1021">
+    <row r="46" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="D46" s="30">
         <v>3</v>
       </c>
@@ -9558,7 +9555,7 @@
         <v>11.94</v>
       </c>
     </row>
-    <row r="47" spans="1:1021">
+    <row r="47" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="D47" s="19"/>
       <c r="E47" s="11"/>
       <c r="F47" s="19"/>
@@ -9577,7 +9574,7 @@
         <v>13.56</v>
       </c>
     </row>
-    <row r="48" spans="1:1021">
+    <row r="48" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="G48" s="30">
         <v>5</v>
       </c>
@@ -9593,7 +9590,7 @@
         <v>15.22</v>
       </c>
     </row>
-    <row r="49" spans="1:1021">
+    <row r="49" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="G49" s="30">
         <v>6</v>
       </c>
@@ -9609,7 +9606,7 @@
         <v>16.82</v>
       </c>
     </row>
-    <row r="50" spans="1:1021">
+    <row r="50" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="G50" s="30">
         <v>7</v>
       </c>
@@ -9625,7 +9622,7 @@
         <v>18.239999999999998</v>
       </c>
     </row>
-    <row r="51" spans="1:1021">
+    <row r="51" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="G51" s="19"/>
       <c r="H51" s="11"/>
       <c r="I51" s="19"/>
@@ -9637,7 +9634,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:1021">
+    <row r="52" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J52" s="30">
         <v>9</v>
       </c>
@@ -9646,7 +9643,7 @@
         <v>21.58</v>
       </c>
     </row>
-    <row r="53" spans="1:1021">
+    <row r="53" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J53" s="30">
         <v>10</v>
       </c>
@@ -9655,7 +9652,7 @@
         <v>23.18</v>
       </c>
     </row>
-    <row r="54" spans="1:1021">
+    <row r="54" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J54" s="30">
         <v>11</v>
       </c>
@@ -9664,7 +9661,7 @@
         <v>24.78</v>
       </c>
     </row>
-    <row r="55" spans="1:1021">
+    <row r="55" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J55" s="30">
         <v>12</v>
       </c>
@@ -9673,7 +9670,7 @@
         <v>26.44</v>
       </c>
     </row>
-    <row r="56" spans="1:1021">
+    <row r="56" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J56" s="30">
         <v>13</v>
       </c>
@@ -9682,7 +9679,7 @@
         <v>28.06</v>
       </c>
     </row>
-    <row r="57" spans="1:1021">
+    <row r="57" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J57" s="30">
         <v>14</v>
       </c>
@@ -9691,7 +9688,7 @@
         <v>29.96</v>
       </c>
     </row>
-    <row r="58" spans="1:1021">
+    <row r="58" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J58" s="30">
         <v>15</v>
       </c>
@@ -9700,28 +9697,28 @@
         <v>32.42</v>
       </c>
     </row>
-    <row r="59" spans="1:1021">
+    <row r="59" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="J59" s="24" t="s">
         <v>55</v>
       </c>
       <c r="K59" s="25"/>
       <c r="L59" s="24"/>
     </row>
-    <row r="60" spans="1:1021" s="32" customFormat="1" ht="25">
-      <c r="A60" s="67" t="s">
+    <row r="60" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
+      <c r="A60" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="67"/>
-      <c r="C60" s="67"/>
-      <c r="D60" s="67"/>
-      <c r="E60" s="67"/>
-      <c r="F60" s="67"/>
-      <c r="G60" s="67"/>
-      <c r="H60" s="67"/>
-      <c r="I60" s="67"/>
-      <c r="J60" s="67"/>
-      <c r="K60" s="67"/>
-      <c r="L60" s="67"/>
+      <c r="B60" s="70"/>
+      <c r="C60" s="70"/>
+      <c r="D60" s="70"/>
+      <c r="E60" s="70"/>
+      <c r="F60" s="70"/>
+      <c r="G60" s="70"/>
+      <c r="H60" s="70"/>
+      <c r="I60" s="70"/>
+      <c r="J60" s="70"/>
+      <c r="K60" s="70"/>
+      <c r="L60" s="70"/>
       <c r="M60" s="31"/>
       <c r="N60" s="31"/>
       <c r="O60" s="31"/>
@@ -10732,27 +10729,27 @@
       <c r="AMF60" s="31"/>
       <c r="AMG60" s="31"/>
     </row>
-    <row r="61" spans="1:1021" s="32" customFormat="1" ht="25">
-      <c r="A61" s="59" t="s">
+    <row r="61" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
+      <c r="A61" s="58" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="60"/>
-      <c r="C61" s="61"/>
-      <c r="D61" s="62" t="s">
+      <c r="B61" s="59"/>
+      <c r="C61" s="60"/>
+      <c r="D61" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="62"/>
-      <c r="F61" s="62"/>
-      <c r="G61" s="62" t="s">
+      <c r="E61" s="57"/>
+      <c r="F61" s="57"/>
+      <c r="G61" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H61" s="62"/>
-      <c r="I61" s="62"/>
-      <c r="J61" s="62" t="s">
+      <c r="H61" s="57"/>
+      <c r="I61" s="57"/>
+      <c r="J61" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="K61" s="62"/>
-      <c r="L61" s="62"/>
+      <c r="K61" s="57"/>
+      <c r="L61" s="57"/>
       <c r="M61" s="31"/>
       <c r="N61" s="31"/>
       <c r="O61" s="31"/>
@@ -11763,7 +11760,7 @@
       <c r="AMF61" s="31"/>
       <c r="AMG61" s="31"/>
     </row>
-    <row r="62" spans="1:1021">
+    <row r="62" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="A62" s="35" t="s">
         <v>50</v>
       </c>
@@ -11801,7 +11798,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="63" spans="1:1021">
+    <row r="63" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="A63" s="35">
         <v>1</v>
       </c>
@@ -11830,7 +11827,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="64" spans="1:1021">
+    <row r="64" spans="1:1021" x14ac:dyDescent="0.2">
       <c r="D64" s="30">
         <v>2</v>
       </c>
@@ -11853,7 +11850,7 @@
         <v>10.039999999999999</v>
       </c>
     </row>
-    <row r="65" spans="4:12">
+    <row r="65" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D65" s="30">
         <v>3</v>
       </c>
@@ -11875,7 +11872,7 @@
         <v>11.94</v>
       </c>
     </row>
-    <row r="66" spans="4:12">
+    <row r="66" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D66" s="19"/>
       <c r="E66" s="11"/>
       <c r="F66" s="19"/>
@@ -11894,7 +11891,7 @@
         <v>13.56</v>
       </c>
     </row>
-    <row r="67" spans="4:12">
+    <row r="67" spans="4:12" x14ac:dyDescent="0.2">
       <c r="G67" s="30">
         <v>5</v>
       </c>
@@ -11910,7 +11907,7 @@
         <v>15.22</v>
       </c>
     </row>
-    <row r="68" spans="4:12">
+    <row r="68" spans="4:12" x14ac:dyDescent="0.2">
       <c r="G68" s="30">
         <v>6</v>
       </c>
@@ -11926,7 +11923,7 @@
         <v>16.82</v>
       </c>
     </row>
-    <row r="69" spans="4:12">
+    <row r="69" spans="4:12" x14ac:dyDescent="0.2">
       <c r="G69" s="30">
         <v>7</v>
       </c>
@@ -11942,7 +11939,7 @@
         <v>18.239999999999998</v>
       </c>
     </row>
-    <row r="70" spans="4:12">
+    <row r="70" spans="4:12" x14ac:dyDescent="0.2">
       <c r="G70" s="19"/>
       <c r="H70" s="11"/>
       <c r="I70" s="19"/>
@@ -11954,7 +11951,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="4:12">
+    <row r="71" spans="4:12" x14ac:dyDescent="0.2">
       <c r="J71" s="30">
         <v>9</v>
       </c>
@@ -11963,7 +11960,7 @@
         <v>21.58</v>
       </c>
     </row>
-    <row r="72" spans="4:12">
+    <row r="72" spans="4:12" x14ac:dyDescent="0.2">
       <c r="J72" s="30">
         <v>10</v>
       </c>
@@ -11972,7 +11969,7 @@
         <v>23.18</v>
       </c>
     </row>
-    <row r="73" spans="4:12">
+    <row r="73" spans="4:12" x14ac:dyDescent="0.2">
       <c r="J73" s="30">
         <v>11</v>
       </c>
@@ -11981,7 +11978,7 @@
         <v>24.78</v>
       </c>
     </row>
-    <row r="74" spans="4:12">
+    <row r="74" spans="4:12" x14ac:dyDescent="0.2">
       <c r="J74" s="30">
         <v>12</v>
       </c>
@@ -11990,7 +11987,7 @@
         <v>26.44</v>
       </c>
     </row>
-    <row r="75" spans="4:12">
+    <row r="75" spans="4:12" x14ac:dyDescent="0.2">
       <c r="J75" s="30">
         <v>13</v>
       </c>
@@ -11999,7 +11996,7 @@
         <v>28.06</v>
       </c>
     </row>
-    <row r="76" spans="4:12">
+    <row r="76" spans="4:12" x14ac:dyDescent="0.2">
       <c r="J76" s="30">
         <v>14</v>
       </c>
@@ -12008,7 +12005,7 @@
         <v>29.96</v>
       </c>
     </row>
-    <row r="77" spans="4:12">
+    <row r="77" spans="4:12" x14ac:dyDescent="0.2">
       <c r="J77" s="30">
         <v>15</v>
       </c>
@@ -12017,23 +12014,13 @@
         <v>32.42</v>
       </c>
     </row>
-    <row r="78" spans="4:12">
+    <row r="78" spans="4:12" x14ac:dyDescent="0.2">
       <c r="J78" s="19"/>
       <c r="K78" s="11"/>
       <c r="L78" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A22:L22"/>
-    <mergeCell ref="A41:L41"/>
-    <mergeCell ref="A60:L60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="G61:I61"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="G42:I42"/>
     <mergeCell ref="D1:L1"/>
     <mergeCell ref="J42:L42"/>
     <mergeCell ref="D23:F23"/>
@@ -12046,6 +12033,16 @@
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A60:L60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="G61:I61"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="G42:I42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -12055,79 +12052,79 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{396D4AB3-D735-C84A-BDAA-B734A45CA873}">
   <dimension ref="A1:L46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.07421875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.69140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.07421875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.69140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.07421875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="25">
-      <c r="A1" s="66" t="s">
+    <row r="1" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A1" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-    </row>
-    <row r="2" spans="1:12" s="6" customFormat="1" ht="59.15" customHeight="1">
-      <c r="A2" s="68" t="s">
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+    </row>
+    <row r="2" spans="1:12" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="70"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="69"/>
       <c r="J2" s="45"/>
       <c r="K2" s="45"/>
       <c r="L2" s="45"/>
     </row>
-    <row r="3" spans="1:12" ht="25">
-      <c r="A3" s="63" t="s">
+    <row r="3" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A3" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="65"/>
-    </row>
-    <row r="4" spans="1:12" ht="25">
-      <c r="A4" s="62" t="s">
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="66"/>
+    </row>
+    <row r="4" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A4" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="59" t="s">
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="60"/>
-      <c r="I4" s="61"/>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="H4" s="59"/>
+      <c r="I4" s="60"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
         <v>50</v>
       </c>
@@ -12156,7 +12153,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="30">
         <v>1</v>
       </c>
@@ -12179,7 +12176,7 @@
         <v>9.6199999999999992</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="30">
         <v>2</v>
       </c>
@@ -12202,7 +12199,7 @@
         <v>13.36</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="30">
         <v>3</v>
       </c>
@@ -12225,7 +12222,7 @@
         <v>16.72</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="30">
         <v>4</v>
       </c>
@@ -12248,7 +12245,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="30">
         <v>5</v>
       </c>
@@ -12271,7 +12268,7 @@
         <v>23.28</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="30">
         <v>6</v>
       </c>
@@ -12294,7 +12291,7 @@
         <v>26.64</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="30">
         <v>7</v>
       </c>
@@ -12317,7 +12314,7 @@
         <v>30.38</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="19"/>
       <c r="B13" s="11"/>
       <c r="C13" s="19"/>
@@ -12328,37 +12325,37 @@
       <c r="H13" s="11"/>
       <c r="I13" s="19"/>
     </row>
-    <row r="14" spans="1:12" ht="25">
-      <c r="A14" s="63" t="s">
+    <row r="14" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A14" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="65"/>
-    </row>
-    <row r="15" spans="1:12" ht="25">
-      <c r="A15" s="62" t="s">
+      <c r="B14" s="65"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="66"/>
+    </row>
+    <row r="15" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A15" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62" t="s">
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="62"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="59" t="s">
+      <c r="E15" s="57"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="H15" s="60"/>
-      <c r="I15" s="61"/>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="H15" s="59"/>
+      <c r="I15" s="60"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="19" t="s">
         <v>50</v>
       </c>
@@ -12387,7 +12384,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="30">
         <v>1</v>
       </c>
@@ -12410,7 +12407,7 @@
         <v>9.6199999999999992</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="30">
         <v>2</v>
       </c>
@@ -12433,7 +12430,7 @@
         <v>13.36</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="30">
         <v>3</v>
       </c>
@@ -12456,7 +12453,7 @@
         <v>16.72</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="30">
         <v>4</v>
       </c>
@@ -12479,7 +12476,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="30">
         <v>5</v>
       </c>
@@ -12502,7 +12499,7 @@
         <v>23.28</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="30">
         <v>6</v>
       </c>
@@ -12525,7 +12522,7 @@
         <v>26.64</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="30">
         <v>7</v>
       </c>
@@ -12548,7 +12545,7 @@
         <v>30.38</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="19"/>
       <c r="B24" s="11"/>
       <c r="C24" s="19"/>
@@ -12559,37 +12556,37 @@
       <c r="H24" s="11"/>
       <c r="I24" s="19"/>
     </row>
-    <row r="25" spans="1:9" ht="25">
-      <c r="A25" s="63" t="s">
+    <row r="25" spans="1:9" ht="27" x14ac:dyDescent="0.2">
+      <c r="A25" s="64" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="64"/>
-      <c r="C25" s="64"/>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64"/>
-      <c r="F25" s="64"/>
-      <c r="G25" s="64"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="65"/>
-    </row>
-    <row r="26" spans="1:9" ht="25">
-      <c r="A26" s="62" t="s">
+      <c r="B25" s="65"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="65"/>
+      <c r="I25" s="66"/>
+    </row>
+    <row r="26" spans="1:9" ht="27" x14ac:dyDescent="0.2">
+      <c r="A26" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="62"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62" t="s">
+      <c r="B26" s="57"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="59" t="s">
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="H26" s="60"/>
-      <c r="I26" s="61"/>
-    </row>
-    <row r="27" spans="1:9">
+      <c r="H26" s="59"/>
+      <c r="I26" s="60"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="19" t="s">
         <v>50</v>
       </c>
@@ -12618,7 +12615,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="30">
         <v>1</v>
       </c>
@@ -12641,7 +12638,7 @@
         <v>9.6199999999999992</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="30">
         <v>2</v>
       </c>
@@ -12664,7 +12661,7 @@
         <v>13.36</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="30">
         <v>3</v>
       </c>
@@ -12687,7 +12684,7 @@
         <v>16.72</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="30">
         <v>4</v>
       </c>
@@ -12710,7 +12707,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="30">
         <v>5</v>
       </c>
@@ -12733,7 +12730,7 @@
         <v>23.28</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="30">
         <v>6</v>
       </c>
@@ -12756,7 +12753,7 @@
         <v>26.64</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="30">
         <v>7</v>
       </c>
@@ -12779,7 +12776,7 @@
         <v>30.38</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="19"/>
       <c r="B35" s="11"/>
       <c r="C35" s="19"/>
@@ -12790,37 +12787,37 @@
       <c r="H35" s="11"/>
       <c r="I35" s="19"/>
     </row>
-    <row r="36" spans="1:9" ht="25">
-      <c r="A36" s="63" t="s">
+    <row r="36" spans="1:9" ht="27" x14ac:dyDescent="0.2">
+      <c r="A36" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="B36" s="64"/>
-      <c r="C36" s="64"/>
-      <c r="D36" s="64"/>
-      <c r="E36" s="64"/>
-      <c r="F36" s="64"/>
-      <c r="G36" s="64"/>
-      <c r="H36" s="64"/>
-      <c r="I36" s="65"/>
-    </row>
-    <row r="37" spans="1:9" ht="25">
-      <c r="A37" s="62" t="s">
+      <c r="B36" s="65"/>
+      <c r="C36" s="65"/>
+      <c r="D36" s="65"/>
+      <c r="E36" s="65"/>
+      <c r="F36" s="65"/>
+      <c r="G36" s="65"/>
+      <c r="H36" s="65"/>
+      <c r="I36" s="66"/>
+    </row>
+    <row r="37" spans="1:9" ht="27" x14ac:dyDescent="0.2">
+      <c r="A37" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="62"/>
-      <c r="C37" s="62"/>
-      <c r="D37" s="62" t="s">
+      <c r="B37" s="57"/>
+      <c r="C37" s="57"/>
+      <c r="D37" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="E37" s="62"/>
-      <c r="F37" s="62"/>
-      <c r="G37" s="59" t="s">
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="H37" s="60"/>
-      <c r="I37" s="61"/>
-    </row>
-    <row r="38" spans="1:9">
+      <c r="H37" s="59"/>
+      <c r="I37" s="60"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="19" t="s">
         <v>50</v>
       </c>
@@ -12849,7 +12846,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="30">
         <v>1</v>
       </c>
@@ -12872,7 +12869,7 @@
         <v>9.6199999999999992</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="30">
         <v>2</v>
       </c>
@@ -12895,7 +12892,7 @@
         <v>13.36</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="30">
         <v>3</v>
       </c>
@@ -12918,7 +12915,7 @@
         <v>16.72</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="30">
         <v>4</v>
       </c>
@@ -12941,7 +12938,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="30">
         <v>5</v>
       </c>
@@ -12964,7 +12961,7 @@
         <v>23.28</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="30">
         <v>6</v>
       </c>
@@ -12987,7 +12984,7 @@
         <v>26.64</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="30">
         <v>7</v>
       </c>
@@ -13010,7 +13007,7 @@
         <v>30.38</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="19"/>
       <c r="B46" s="11"/>
       <c r="C46" s="19"/>
@@ -13023,6 +13020,12 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A2:I2"/>
     <mergeCell ref="A36:I36"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="D37:F37"/>
@@ -13035,12 +13038,6 @@
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="D26:F26"/>
     <mergeCell ref="G26:I26"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13049,23 +13046,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AMJ73"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.07421875" defaultRowHeight="15.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="58" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="7.69140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.07421875" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="11.07421875" style="6"/>
+    <col min="2" max="3" width="7.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="11" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1024" ht="25">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
+      <c r="A1" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-    </row>
-    <row r="2" spans="1:1024">
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+    </row>
+    <row r="2" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
         <v>40</v>
       </c>
@@ -13083,7 +13080,7 @@
       <c r="Q2" s="16"/>
       <c r="R2" s="16"/>
     </row>
-    <row r="3" spans="1:1024">
+    <row r="3" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
         <v>1.0668</v>
       </c>
@@ -14117,13 +14114,13 @@
       <c r="AMI3" s="10"/>
       <c r="AMJ3" s="10"/>
     </row>
-    <row r="4" spans="1:1024" ht="25">
-      <c r="A4" s="50" t="s">
+    <row r="4" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
+      <c r="A4" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="J4" s="7"/>
@@ -14134,7 +14131,7 @@
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
     </row>
-    <row r="5" spans="1:1024">
+    <row r="5" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>40</v>
       </c>
@@ -14157,7 +14154,7 @@
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
     </row>
-    <row r="6" spans="1:1024">
+    <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="11">
         <v>1.0668</v>
       </c>
@@ -15191,13 +15188,13 @@
       <c r="AMI6" s="10"/>
       <c r="AMJ6" s="10"/>
     </row>
-    <row r="7" spans="1:1024" ht="25">
-      <c r="A7" s="50" t="s">
+    <row r="7" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
+      <c r="A7" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="J7" s="7"/>
@@ -15208,7 +15205,7 @@
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
     </row>
-    <row r="8" spans="1:1024">
+    <row r="8" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
         <v>40</v>
       </c>
@@ -15231,7 +15228,7 @@
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
     </row>
-    <row r="9" spans="1:1024">
+    <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="11"/>
       <c r="B9" s="40"/>
       <c r="C9" s="40"/>
@@ -16257,13 +16254,13 @@
       <c r="AMI9" s="10"/>
       <c r="AMJ9" s="10"/>
     </row>
-    <row r="10" spans="1:1024" ht="25">
-      <c r="A10" s="50" t="s">
+    <row r="10" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
+      <c r="A10" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
       <c r="G10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
@@ -16273,7 +16270,7 @@
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
     </row>
-    <row r="11" spans="1:1024">
+    <row r="11" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A11" s="17" t="s">
         <v>40</v>
       </c>
@@ -16294,7 +16291,7 @@
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
     </row>
-    <row r="12" spans="1:1024">
+    <row r="12" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A12" s="11">
         <v>1.0668</v>
       </c>
@@ -17328,7 +17325,7 @@
       <c r="AMI12" s="10"/>
       <c r="AMJ12" s="10"/>
     </row>
-    <row r="13" spans="1:1024">
+    <row r="13" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
@@ -17337,13 +17334,13 @@
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
     </row>
-    <row r="14" spans="1:1024" ht="25">
-      <c r="A14" s="51" t="s">
+    <row r="14" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
+      <c r="A14" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
@@ -17352,7 +17349,7 @@
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
     </row>
-    <row r="15" spans="1:1024">
+    <row r="15" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
@@ -17361,7 +17358,7 @@
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
     </row>
-    <row r="16" spans="1:1024">
+    <row r="16" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
       <c r="M16" s="8"/>
@@ -17370,24 +17367,24 @@
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
     </row>
-    <row r="17" spans="2:18">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="7"/>
     </row>
-    <row r="18" spans="2:18">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
       <c r="R18" s="7"/>
     </row>
-    <row r="19" spans="2:18">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
     </row>
-    <row r="20" spans="2:18">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
@@ -17400,7 +17397,7 @@
       <c r="Q20" s="7"/>
       <c r="R20" s="7"/>
     </row>
-    <row r="21" spans="2:18">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
@@ -17413,7 +17410,7 @@
       <c r="Q21" s="7"/>
       <c r="R21" s="7"/>
     </row>
-    <row r="22" spans="2:18">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
@@ -17426,7 +17423,7 @@
       <c r="Q22" s="7"/>
       <c r="R22" s="7"/>
     </row>
-    <row r="23" spans="2:18">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="G23" s="7"/>
@@ -17438,7 +17435,7 @@
       <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
     </row>
-    <row r="24" spans="2:18">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
       <c r="J24" s="7"/>
@@ -17448,7 +17445,7 @@
       <c r="Q24" s="7"/>
       <c r="R24" s="7"/>
     </row>
-    <row r="25" spans="2:18">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
       <c r="J25" s="7"/>
@@ -17458,7 +17455,7 @@
       <c r="Q25" s="7"/>
       <c r="R25" s="7"/>
     </row>
-    <row r="26" spans="2:18">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
       <c r="J26" s="7"/>
@@ -17468,7 +17465,7 @@
       <c r="Q26" s="7"/>
       <c r="R26" s="7"/>
     </row>
-    <row r="27" spans="2:18">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
       <c r="J27" s="7"/>
@@ -17478,7 +17475,7 @@
       <c r="Q27" s="7"/>
       <c r="R27" s="7"/>
     </row>
-    <row r="28" spans="2:18">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
@@ -17486,7 +17483,7 @@
       <c r="Q28" s="7"/>
       <c r="R28" s="7"/>
     </row>
-    <row r="29" spans="2:18">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G29" s="7"/>
       <c r="J29" s="7"/>
       <c r="K29" s="7"/>
@@ -17495,7 +17492,7 @@
       <c r="Q29" s="7"/>
       <c r="R29" s="7"/>
     </row>
-    <row r="30" spans="2:18">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
@@ -17503,7 +17500,7 @@
       <c r="Q30" s="7"/>
       <c r="R30" s="7"/>
     </row>
-    <row r="31" spans="2:18">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J31" s="7"/>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -17511,7 +17508,7 @@
       <c r="Q31" s="7"/>
       <c r="R31" s="7"/>
     </row>
-    <row r="32" spans="2:18">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
@@ -17519,7 +17516,7 @@
       <c r="Q32" s="7"/>
       <c r="R32" s="7"/>
     </row>
-    <row r="33" spans="2:18">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -17527,7 +17524,7 @@
       <c r="Q33" s="7"/>
       <c r="R33" s="7"/>
     </row>
-    <row r="34" spans="2:18">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
@@ -17535,19 +17532,19 @@
       <c r="Q34" s="7"/>
       <c r="R34" s="7"/>
     </row>
-    <row r="35" spans="2:18">
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
       <c r="P35" s="7"/>
       <c r="Q35" s="7"/>
       <c r="R35" s="7"/>
     </row>
-    <row r="36" spans="2:18">
+    <row r="36" spans="2:18" x14ac:dyDescent="0.2">
       <c r="P36" s="7"/>
       <c r="Q36" s="7"/>
       <c r="R36" s="7"/>
     </row>
-    <row r="39" spans="2:18">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -17557,7 +17554,7 @@
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
     </row>
-    <row r="40" spans="2:18">
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
@@ -17567,7 +17564,7 @@
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
     </row>
-    <row r="41" spans="2:18">
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -17577,7 +17574,7 @@
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
     </row>
-    <row r="42" spans="2:18">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="G42" s="7"/>
@@ -17586,75 +17583,75 @@
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
     </row>
-    <row r="43" spans="2:18">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G43" s="7"/>
       <c r="H43" s="7"/>
       <c r="J43" s="7"/>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
     </row>
-    <row r="44" spans="2:18">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
       <c r="J44" s="7"/>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
     </row>
-    <row r="45" spans="2:18">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G45" s="7"/>
       <c r="H45" s="7"/>
       <c r="J45" s="7"/>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
     </row>
-    <row r="46" spans="2:18">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
       <c r="J46" s="7"/>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
     </row>
-    <row r="47" spans="2:18">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J47" s="7"/>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
     </row>
-    <row r="48" spans="2:18">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="G48" s="7"/>
       <c r="J48" s="7"/>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
     </row>
-    <row r="49" spans="2:12">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J49" s="7"/>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
     </row>
-    <row r="50" spans="2:12">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J50" s="7"/>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
     </row>
-    <row r="51" spans="2:12">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
     </row>
-    <row r="52" spans="2:12">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J52" s="7"/>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
     </row>
-    <row r="53" spans="2:12">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J53" s="7"/>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
     </row>
-    <row r="54" spans="2:12">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.2">
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
     </row>
-    <row r="58" spans="2:12">
+    <row r="58" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
@@ -17664,7 +17661,7 @@
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
     </row>
-    <row r="59" spans="2:12">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
@@ -17674,7 +17671,7 @@
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
     </row>
-    <row r="60" spans="2:12">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
@@ -17684,7 +17681,7 @@
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
     </row>
-    <row r="61" spans="2:12">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
       <c r="G61" s="7"/>
@@ -17693,71 +17690,71 @@
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
     </row>
-    <row r="62" spans="2:12">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.2">
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
       <c r="J62" s="7"/>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
     </row>
-    <row r="63" spans="2:12">
+    <row r="63" spans="2:12" x14ac:dyDescent="0.2">
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
       <c r="J63" s="7"/>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
     </row>
-    <row r="64" spans="2:12">
+    <row r="64" spans="2:12" x14ac:dyDescent="0.2">
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
     </row>
-    <row r="65" spans="7:12">
+    <row r="65" spans="7:12" x14ac:dyDescent="0.2">
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
     </row>
-    <row r="66" spans="7:12">
+    <row r="66" spans="7:12" x14ac:dyDescent="0.2">
       <c r="J66" s="7"/>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
     </row>
-    <row r="67" spans="7:12">
+    <row r="67" spans="7:12" x14ac:dyDescent="0.2">
       <c r="G67" s="7"/>
       <c r="J67" s="7"/>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
     </row>
-    <row r="68" spans="7:12">
+    <row r="68" spans="7:12" x14ac:dyDescent="0.2">
       <c r="J68" s="7"/>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
     </row>
-    <row r="69" spans="7:12">
+    <row r="69" spans="7:12" x14ac:dyDescent="0.2">
       <c r="J69" s="7"/>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
     </row>
-    <row r="70" spans="7:12">
+    <row r="70" spans="7:12" x14ac:dyDescent="0.2">
       <c r="J70" s="7"/>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
     </row>
-    <row r="71" spans="7:12">
+    <row r="71" spans="7:12" x14ac:dyDescent="0.2">
       <c r="J71" s="7"/>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
     </row>
-    <row r="72" spans="7:12">
+    <row r="72" spans="7:12" x14ac:dyDescent="0.2">
       <c r="J72" s="7"/>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
     </row>
-    <row r="73" spans="7:12">
+    <row r="73" spans="7:12" x14ac:dyDescent="0.2">
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
     </row>
@@ -17777,23 +17774,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E0F765-C5B1-654D-95FF-016841AE7F76}">
   <dimension ref="A1:AMJ57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.07421875" defaultRowHeight="15.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="58" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="7.69140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.07421875" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="1024" width="11.07421875" style="9"/>
+    <col min="2" max="3" width="7.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="1024" width="11" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="25">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:18" ht="27" x14ac:dyDescent="0.2">
+      <c r="A1" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="55"/>
-    </row>
-    <row r="2" spans="1:18">
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="56"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
         <v>40</v>
       </c>
@@ -17820,7 +17817,7 @@
       <c r="Q2" s="13"/>
       <c r="R2" s="13"/>
     </row>
-    <row r="3" spans="1:18" s="9" customFormat="1">
+    <row r="3" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -17832,19 +17829,19 @@
       <c r="I3" s="10"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:18" s="9" customFormat="1" ht="25">
-      <c r="A4" s="53" t="s">
+    <row r="4" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A4" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="55"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="56"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="I4" s="10"/>
       <c r="O4" s="10"/>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1">
+    <row r="5" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
         <v>40</v>
       </c>
@@ -17862,7 +17859,7 @@
       <c r="I5" s="10"/>
       <c r="O5" s="10"/>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1">
+    <row r="6" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11">
         <v>1</v>
       </c>
@@ -17876,13 +17873,13 @@
       <c r="I6" s="10"/>
       <c r="O6" s="10"/>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="25">
-      <c r="A7" s="53" t="s">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A7" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="55"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="56"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
@@ -17890,7 +17887,7 @@
       <c r="I7" s="10"/>
       <c r="O7" s="10"/>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1">
+    <row r="8" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="19" t="s">
         <v>40</v>
       </c>
@@ -17910,7 +17907,7 @@
       <c r="I8" s="10"/>
       <c r="O8" s="10"/>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1">
+    <row r="9" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <v>1</v>
       </c>
@@ -17929,13 +17926,13 @@
       <c r="N9" s="10"/>
       <c r="O9" s="10"/>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="25">
-      <c r="A10" s="53" t="s">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A10" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="55"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="56"/>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="I10" s="10"/>
@@ -17943,7 +17940,7 @@
       <c r="N10" s="10"/>
       <c r="O10" s="10"/>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1">
+    <row r="11" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
         <v>40</v>
       </c>
@@ -17963,7 +17960,7 @@
       <c r="N11" s="10"/>
       <c r="O11" s="10"/>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1">
+    <row r="12" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="11">
         <v>1</v>
       </c>
@@ -17977,7 +17974,7 @@
       <c r="N12" s="10"/>
       <c r="O12" s="10"/>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1">
+    <row r="13" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -17991,13 +17988,13 @@
       <c r="N13" s="10"/>
       <c r="O13" s="10"/>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="25">
-      <c r="A14" s="52" t="s">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A14" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="52"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
@@ -18007,13 +18004,13 @@
       <c r="N14" s="10"/>
       <c r="O14" s="10"/>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="25">
-      <c r="A15" s="52" t="s">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A15" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="52"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
@@ -18023,7 +18020,7 @@
       <c r="N15" s="10"/>
       <c r="O15" s="10"/>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1">
+    <row r="16" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -18037,7 +18034,7 @@
       <c r="N16" s="10"/>
       <c r="O16" s="10"/>
     </row>
-    <row r="17" spans="1:15" s="9" customFormat="1">
+    <row r="17" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -18051,7 +18048,7 @@
       <c r="N17" s="10"/>
       <c r="O17" s="10"/>
     </row>
-    <row r="18" spans="1:15" s="9" customFormat="1">
+    <row r="18" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -18065,7 +18062,7 @@
       <c r="N18" s="10"/>
       <c r="O18" s="10"/>
     </row>
-    <row r="19" spans="1:15" s="9" customFormat="1">
+    <row r="19" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
@@ -18081,12 +18078,12 @@
       <c r="N19" s="10"/>
       <c r="O19" s="10"/>
     </row>
-    <row r="20" spans="1:15" s="9" customFormat="1">
+    <row r="20" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
       <c r="O20" s="10"/>
     </row>
-    <row r="21" spans="1:15" s="9" customFormat="1">
+    <row r="21" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -18102,7 +18099,7 @@
       <c r="M21" s="10"/>
       <c r="N21" s="10"/>
     </row>
-    <row r="22" spans="1:15" s="9" customFormat="1">
+    <row r="22" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10"/>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
@@ -18118,7 +18115,7 @@
       <c r="M22" s="10"/>
       <c r="N22" s="10"/>
     </row>
-    <row r="23" spans="1:15" s="9" customFormat="1">
+    <row r="23" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10"/>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
@@ -18126,19 +18123,19 @@
       <c r="M23" s="10"/>
       <c r="N23" s="10"/>
     </row>
-    <row r="24" spans="1:15" s="9" customFormat="1">
+    <row r="24" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="I24" s="10"/>
     </row>
-    <row r="25" spans="1:15" s="9" customFormat="1">
+    <row r="25" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="10"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="I25" s="10"/>
     </row>
-    <row r="26" spans="1:15" s="9" customFormat="1">
+    <row r="26" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
@@ -18147,7 +18144,7 @@
       <c r="F26" s="10"/>
       <c r="I26" s="10"/>
     </row>
-    <row r="27" spans="1:15" s="9" customFormat="1">
+    <row r="27" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
@@ -18156,7 +18153,7 @@
       <c r="F27" s="10"/>
       <c r="I27" s="10"/>
     </row>
-    <row r="28" spans="1:15" s="9" customFormat="1">
+    <row r="28" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
@@ -18165,7 +18162,7 @@
       <c r="F28" s="10"/>
       <c r="I28" s="10"/>
     </row>
-    <row r="29" spans="1:15" s="9" customFormat="1">
+    <row r="29" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
@@ -18174,7 +18171,7 @@
       <c r="F29" s="10"/>
       <c r="I29" s="10"/>
     </row>
-    <row r="30" spans="1:15" s="9" customFormat="1">
+    <row r="30" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -18185,7 +18182,7 @@
       <c r="H30" s="10"/>
       <c r="I30" s="10"/>
     </row>
-    <row r="31" spans="1:15" s="9" customFormat="1">
+    <row r="31" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="10"/>
       <c r="B31" s="10"/>
       <c r="C31" s="10"/>
@@ -18196,7 +18193,7 @@
       <c r="H31" s="10"/>
       <c r="I31" s="10"/>
     </row>
-    <row r="32" spans="1:15" s="9" customFormat="1">
+    <row r="32" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="10"/>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
@@ -18207,7 +18204,7 @@
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
     </row>
-    <row r="33" spans="1:12" s="9" customFormat="1">
+    <row r="33" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
@@ -18218,7 +18215,7 @@
       <c r="H33" s="10"/>
       <c r="I33" s="10"/>
     </row>
-    <row r="34" spans="1:12" s="9" customFormat="1">
+    <row r="34" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
@@ -18229,7 +18226,7 @@
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
     </row>
-    <row r="35" spans="1:12" s="9" customFormat="1">
+    <row r="35" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
@@ -18240,7 +18237,7 @@
       <c r="H35" s="10"/>
       <c r="I35" s="10"/>
     </row>
-    <row r="36" spans="1:12" s="9" customFormat="1">
+    <row r="36" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
@@ -18251,7 +18248,7 @@
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
     </row>
-    <row r="37" spans="1:12" s="9" customFormat="1">
+    <row r="37" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
@@ -18262,13 +18259,13 @@
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
     </row>
-    <row r="38" spans="1:12" s="9" customFormat="1">
+    <row r="38" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
       <c r="L38" s="10"/>
     </row>
-    <row r="40" spans="1:12" s="9" customFormat="1">
+    <row r="40" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
@@ -18282,7 +18279,7 @@
       <c r="K40" s="12"/>
       <c r="L40" s="12"/>
     </row>
-    <row r="41" spans="1:12" s="9" customFormat="1">
+    <row r="41" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
@@ -18296,25 +18293,25 @@
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
     </row>
-    <row r="42" spans="1:12" s="9" customFormat="1">
+    <row r="42" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="10"/>
       <c r="E42" s="10"/>
       <c r="F42" s="10"/>
       <c r="I42" s="10"/>
     </row>
-    <row r="43" spans="1:12" s="9" customFormat="1">
+    <row r="43" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="10"/>
       <c r="E43" s="10"/>
       <c r="F43" s="10"/>
       <c r="I43" s="10"/>
     </row>
-    <row r="44" spans="1:12" s="9" customFormat="1">
+    <row r="44" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="10"/>
       <c r="E44" s="10"/>
       <c r="F44" s="10"/>
       <c r="I44" s="10"/>
     </row>
-    <row r="45" spans="1:12" s="9" customFormat="1">
+    <row r="45" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="10"/>
@@ -18323,7 +18320,7 @@
       <c r="F45" s="10"/>
       <c r="I45" s="10"/>
     </row>
-    <row r="46" spans="1:12" s="9" customFormat="1">
+    <row r="46" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="10"/>
@@ -18332,7 +18329,7 @@
       <c r="F46" s="10"/>
       <c r="I46" s="10"/>
     </row>
-    <row r="47" spans="1:12" s="9" customFormat="1">
+    <row r="47" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="10"/>
@@ -18341,7 +18338,7 @@
       <c r="F47" s="10"/>
       <c r="I47" s="10"/>
     </row>
-    <row r="48" spans="1:12" s="9" customFormat="1">
+    <row r="48" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="10"/>
@@ -18350,7 +18347,7 @@
       <c r="F48" s="10"/>
       <c r="I48" s="10"/>
     </row>
-    <row r="49" spans="1:12" s="9" customFormat="1">
+    <row r="49" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="10"/>
@@ -18361,7 +18358,7 @@
       <c r="H49" s="10"/>
       <c r="I49" s="10"/>
     </row>
-    <row r="50" spans="1:12" s="9" customFormat="1">
+    <row r="50" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="10"/>
@@ -18372,7 +18369,7 @@
       <c r="H50" s="10"/>
       <c r="I50" s="10"/>
     </row>
-    <row r="51" spans="1:12" s="9" customFormat="1">
+    <row r="51" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="10"/>
@@ -18383,7 +18380,7 @@
       <c r="H51" s="10"/>
       <c r="I51" s="10"/>
     </row>
-    <row r="52" spans="1:12" s="9" customFormat="1">
+    <row r="52" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="10"/>
@@ -18394,7 +18391,7 @@
       <c r="H52" s="10"/>
       <c r="I52" s="10"/>
     </row>
-    <row r="53" spans="1:12" s="9" customFormat="1">
+    <row r="53" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="10"/>
@@ -18405,7 +18402,7 @@
       <c r="H53" s="10"/>
       <c r="I53" s="10"/>
     </row>
-    <row r="54" spans="1:12" s="9" customFormat="1">
+    <row r="54" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="10"/>
@@ -18416,7 +18413,7 @@
       <c r="H54" s="10"/>
       <c r="I54" s="10"/>
     </row>
-    <row r="55" spans="1:12" s="9" customFormat="1">
+    <row r="55" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="10"/>
@@ -18427,7 +18424,7 @@
       <c r="H55" s="10"/>
       <c r="I55" s="10"/>
     </row>
-    <row r="56" spans="1:12" s="9" customFormat="1">
+    <row r="56" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
@@ -18438,7 +18435,7 @@
       <c r="H56" s="10"/>
       <c r="I56" s="10"/>
     </row>
-    <row r="57" spans="1:12" s="9" customFormat="1">
+    <row r="57" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="I57" s="10"/>
       <c r="J57" s="10"/>
       <c r="K57" s="10"/>
@@ -18461,23 +18458,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AMJ69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.07421875" defaultRowHeight="15.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="58" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="7.69140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.07421875" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="1024" width="11.07421875" style="9"/>
+    <col min="2" max="3" width="7.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="1024" width="11" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="25">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:18" ht="27" x14ac:dyDescent="0.2">
+      <c r="A1" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="55"/>
-    </row>
-    <row r="2" spans="1:18">
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="56"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
         <v>40</v>
       </c>
@@ -18504,7 +18501,7 @@
       <c r="Q2" s="13"/>
       <c r="R2" s="13"/>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
         <v>0</v>
       </c>
@@ -18525,7 +18522,7 @@
       <c r="Q3" s="10"/>
       <c r="R3" s="10"/>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="11">
         <v>0.5</v>
       </c>
@@ -18537,7 +18534,7 @@
       <c r="I4" s="10"/>
       <c r="O4" s="10"/>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
         <v>1.5</v>
       </c>
@@ -18549,7 +18546,7 @@
       <c r="I5" s="10"/>
       <c r="O5" s="10"/>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="11">
         <v>-1</v>
       </c>
@@ -18561,19 +18558,19 @@
       <c r="I6" s="10"/>
       <c r="O6" s="10"/>
     </row>
-    <row r="7" spans="1:18" ht="25">
-      <c r="A7" s="53" t="s">
+    <row r="7" spans="1:18" ht="27" x14ac:dyDescent="0.2">
+      <c r="A7" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="55"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="56"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="I7" s="10"/>
       <c r="O7" s="10"/>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="19" t="s">
         <v>40</v>
       </c>
@@ -18591,7 +18588,7 @@
       <c r="I8" s="10"/>
       <c r="O8" s="10"/>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <v>0</v>
       </c>
@@ -18605,7 +18602,7 @@
       <c r="I9" s="10"/>
       <c r="O9" s="10"/>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="11">
         <v>0.5</v>
       </c>
@@ -18619,7 +18616,7 @@
       <c r="I10" s="10"/>
       <c r="O10" s="10"/>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="11">
         <v>1.5</v>
       </c>
@@ -18633,7 +18630,7 @@
       <c r="I11" s="10"/>
       <c r="O11" s="10"/>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="11">
         <v>-1</v>
       </c>
@@ -18647,13 +18644,13 @@
       <c r="I12" s="10"/>
       <c r="O12" s="10"/>
     </row>
-    <row r="13" spans="1:18" ht="25">
-      <c r="A13" s="53" t="s">
+    <row r="13" spans="1:18" ht="27" x14ac:dyDescent="0.2">
+      <c r="A13" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="55"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="56"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
@@ -18661,7 +18658,7 @@
       <c r="I13" s="10"/>
       <c r="O13" s="10"/>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="19" t="s">
         <v>40</v>
       </c>
@@ -18681,7 +18678,7 @@
       <c r="I14" s="10"/>
       <c r="O14" s="10"/>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="11">
         <v>0</v>
       </c>
@@ -18700,7 +18697,7 @@
       <c r="N15" s="15"/>
       <c r="O15" s="10"/>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="11">
         <v>0.5</v>
       </c>
@@ -18711,7 +18708,7 @@
       <c r="N16" s="15"/>
       <c r="O16" s="10"/>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="11">
         <v>1.5</v>
       </c>
@@ -18730,7 +18727,7 @@
       <c r="N17" s="10"/>
       <c r="O17" s="10"/>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="11">
         <v>-1</v>
       </c>
@@ -18744,13 +18741,13 @@
       <c r="N18" s="10"/>
       <c r="O18" s="10"/>
     </row>
-    <row r="19" spans="1:15" ht="25">
-      <c r="A19" s="53" t="s">
+    <row r="19" spans="1:15" ht="27" x14ac:dyDescent="0.2">
+      <c r="A19" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="55"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="56"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="I19" s="10"/>
@@ -18758,7 +18755,7 @@
       <c r="N19" s="10"/>
       <c r="O19" s="10"/>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="19" t="s">
         <v>40</v>
       </c>
@@ -18778,7 +18775,7 @@
       <c r="N20" s="10"/>
       <c r="O20" s="10"/>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="11">
         <v>0</v>
       </c>
@@ -18792,7 +18789,7 @@
       <c r="N21" s="10"/>
       <c r="O21" s="10"/>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="11">
         <v>0.5</v>
       </c>
@@ -18806,7 +18803,7 @@
       <c r="N22" s="10"/>
       <c r="O22" s="10"/>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="11">
         <v>1.5</v>
       </c>
@@ -18822,7 +18819,7 @@
       <c r="N23" s="10"/>
       <c r="O23" s="10"/>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="11">
         <v>-1</v>
       </c>
@@ -18838,7 +18835,7 @@
       <c r="N24" s="10"/>
       <c r="O24" s="10"/>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
@@ -18852,13 +18849,13 @@
       <c r="N25" s="10"/>
       <c r="O25" s="10"/>
     </row>
-    <row r="26" spans="1:15" ht="25">
-      <c r="A26" s="52" t="s">
+    <row r="26" spans="1:15" ht="27" x14ac:dyDescent="0.2">
+      <c r="A26" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="52"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="52"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -18868,13 +18865,13 @@
       <c r="N26" s="10"/>
       <c r="O26" s="10"/>
     </row>
-    <row r="27" spans="1:15" ht="25">
-      <c r="A27" s="52" t="s">
+    <row r="27" spans="1:15" ht="27" x14ac:dyDescent="0.2">
+      <c r="A27" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="52"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="52"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -18884,7 +18881,7 @@
       <c r="N27" s="10"/>
       <c r="O27" s="10"/>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
@@ -18898,7 +18895,7 @@
       <c r="N28" s="10"/>
       <c r="O28" s="10"/>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
@@ -18912,7 +18909,7 @@
       <c r="N29" s="10"/>
       <c r="O29" s="10"/>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -18926,7 +18923,7 @@
       <c r="N30" s="10"/>
       <c r="O30" s="10"/>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B31" s="10"/>
       <c r="C31" s="10"/>
       <c r="D31" s="10"/>
@@ -18942,12 +18939,12 @@
       <c r="N31" s="10"/>
       <c r="O31" s="10"/>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="M32" s="10"/>
       <c r="N32" s="10"/>
       <c r="O32" s="10"/>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="12"/>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
@@ -18963,7 +18960,7 @@
       <c r="M33" s="10"/>
       <c r="N33" s="10"/>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
@@ -18979,7 +18976,7 @@
       <c r="M34" s="10"/>
       <c r="N34" s="10"/>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" s="10"/>
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
@@ -18987,19 +18984,19 @@
       <c r="M35" s="10"/>
       <c r="N35" s="10"/>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="10"/>
       <c r="E36" s="10"/>
       <c r="F36" s="10"/>
       <c r="I36" s="10"/>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" s="10"/>
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
       <c r="I37" s="10"/>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
@@ -19008,7 +19005,7 @@
       <c r="F38" s="10"/>
       <c r="I38" s="10"/>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="10"/>
@@ -19017,7 +19014,7 @@
       <c r="F39" s="10"/>
       <c r="I39" s="10"/>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="10"/>
@@ -19026,7 +19023,7 @@
       <c r="F40" s="10"/>
       <c r="I40" s="10"/>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
@@ -19035,7 +19032,7 @@
       <c r="F41" s="10"/>
       <c r="I41" s="10"/>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
@@ -19046,7 +19043,7 @@
       <c r="H42" s="10"/>
       <c r="I42" s="10"/>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="10"/>
@@ -19057,7 +19054,7 @@
       <c r="H43" s="10"/>
       <c r="I43" s="10"/>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="10"/>
@@ -19068,7 +19065,7 @@
       <c r="H44" s="10"/>
       <c r="I44" s="10"/>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="10"/>
@@ -19079,7 +19076,7 @@
       <c r="H45" s="10"/>
       <c r="I45" s="10"/>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="10"/>
@@ -19090,7 +19087,7 @@
       <c r="H46" s="10"/>
       <c r="I46" s="10"/>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="10"/>
@@ -19101,7 +19098,7 @@
       <c r="H47" s="10"/>
       <c r="I47" s="10"/>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="10"/>
@@ -19112,7 +19109,7 @@
       <c r="H48" s="10"/>
       <c r="I48" s="10"/>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="10"/>
@@ -19123,13 +19120,13 @@
       <c r="H49" s="10"/>
       <c r="I49" s="10"/>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="I50" s="10"/>
       <c r="J50" s="10"/>
       <c r="K50" s="10"/>
       <c r="L50" s="10"/>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="12"/>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
@@ -19143,7 +19140,7 @@
       <c r="K52" s="12"/>
       <c r="L52" s="12"/>
     </row>
-    <row r="53" spans="1:12">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="10"/>
@@ -19157,25 +19154,25 @@
       <c r="K53" s="10"/>
       <c r="L53" s="10"/>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" s="10"/>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
       <c r="I54" s="10"/>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="10"/>
       <c r="E55" s="10"/>
       <c r="F55" s="10"/>
       <c r="I55" s="10"/>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="10"/>
       <c r="E56" s="10"/>
       <c r="F56" s="10"/>
       <c r="I56" s="10"/>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="10"/>
@@ -19184,7 +19181,7 @@
       <c r="F57" s="10"/>
       <c r="I57" s="10"/>
     </row>
-    <row r="58" spans="1:12">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="10"/>
       <c r="B58" s="10"/>
       <c r="C58" s="10"/>
@@ -19193,7 +19190,7 @@
       <c r="F58" s="10"/>
       <c r="I58" s="10"/>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="10"/>
       <c r="B59" s="10"/>
       <c r="C59" s="10"/>
@@ -19202,7 +19199,7 @@
       <c r="F59" s="10"/>
       <c r="I59" s="10"/>
     </row>
-    <row r="60" spans="1:12">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="10"/>
       <c r="B60" s="10"/>
       <c r="C60" s="10"/>
@@ -19211,7 +19208,7 @@
       <c r="F60" s="10"/>
       <c r="I60" s="10"/>
     </row>
-    <row r="61" spans="1:12">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="10"/>
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
@@ -19222,7 +19219,7 @@
       <c r="H61" s="10"/>
       <c r="I61" s="10"/>
     </row>
-    <row r="62" spans="1:12">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="10"/>
       <c r="B62" s="10"/>
       <c r="C62" s="10"/>
@@ -19233,7 +19230,7 @@
       <c r="H62" s="10"/>
       <c r="I62" s="10"/>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="10"/>
       <c r="B63" s="10"/>
       <c r="C63" s="10"/>
@@ -19244,7 +19241,7 @@
       <c r="H63" s="10"/>
       <c r="I63" s="10"/>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="10"/>
       <c r="B64" s="10"/>
       <c r="C64" s="10"/>
@@ -19255,7 +19252,7 @@
       <c r="H64" s="10"/>
       <c r="I64" s="10"/>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="10"/>
       <c r="B65" s="10"/>
       <c r="C65" s="10"/>
@@ -19266,7 +19263,7 @@
       <c r="H65" s="10"/>
       <c r="I65" s="10"/>
     </row>
-    <row r="66" spans="1:12">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="10"/>
       <c r="B66" s="10"/>
       <c r="C66" s="10"/>
@@ -19277,7 +19274,7 @@
       <c r="H66" s="10"/>
       <c r="I66" s="10"/>
     </row>
-    <row r="67" spans="1:12">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="10"/>
       <c r="B67" s="10"/>
       <c r="C67" s="10"/>
@@ -19288,7 +19285,7 @@
       <c r="H67" s="10"/>
       <c r="I67" s="10"/>
     </row>
-    <row r="68" spans="1:12">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="10"/>
       <c r="B68" s="10"/>
       <c r="C68" s="10"/>
@@ -19299,7 +19296,7 @@
       <c r="H68" s="10"/>
       <c r="I68" s="10"/>
     </row>
-    <row r="69" spans="1:12">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="I69" s="10"/>
       <c r="J69" s="10"/>
       <c r="K69" s="10"/>
@@ -19322,82 +19319,82 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EA0DC49-B228-6142-89A2-F876D0182B62}">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.69140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.07421875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.07421875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.07421875" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" style="6" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.07421875" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.83203125" style="6" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="25" style="6" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="11" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25">
-      <c r="A1" s="56" t="s">
+    <row r="1" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A1" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="58"/>
-    </row>
-    <row r="2" spans="1:13" ht="25">
-      <c r="A2" s="62" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="63"/>
+    </row>
+    <row r="2" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A2" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-    </row>
-    <row r="3" spans="1:13" ht="25">
-      <c r="A3" s="62" t="s">
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+    </row>
+    <row r="3" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A3" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62" t="s">
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="59" t="s">
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="60"/>
-      <c r="J3" s="61"/>
-      <c r="K3" s="59" t="s">
+      <c r="I3" s="59"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="60"/>
-      <c r="M3" s="61"/>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="L3" s="59"/>
+      <c r="M3" s="60"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="17"/>
       <c r="B4" s="19" t="s">
         <v>51</v>
@@ -19436,7 +19433,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
         <v>55</v>
       </c>
@@ -19453,51 +19450,49 @@
         <v>0.114917376</v>
       </c>
       <c r="L5" s="25"/>
-      <c r="M5" s="25">
-        <v>9.6127163999999987E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25">
-      <c r="A6" s="63" t="s">
+      <c r="M5" s="25"/>
+    </row>
+    <row r="6" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A6" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="65"/>
-    </row>
-    <row r="7" spans="1:13" ht="25">
-      <c r="A7" s="62" t="s">
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="66"/>
+    </row>
+    <row r="7" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A7" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="62" t="s">
+      <c r="B7" s="57"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="59" t="s">
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="60"/>
-      <c r="J7" s="61"/>
-      <c r="K7" s="59" t="s">
+      <c r="I7" s="59"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="60"/>
-      <c r="M7" s="61"/>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="L7" s="59"/>
+      <c r="M7" s="60"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
       <c r="B8" s="19" t="s">
         <v>51</v>
@@ -19536,7 +19531,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
         <v>55</v>
       </c>
@@ -19552,54 +19547,50 @@
       <c r="K9" s="25">
         <v>0.11529621600000001</v>
       </c>
-      <c r="L9" s="25">
-        <v>5.5062251999999999E-2</v>
-      </c>
-      <c r="M9" s="25">
-        <v>9.6979218000000002E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="25">
-      <c r="A10" s="62" t="s">
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+    </row>
+    <row r="10" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A10" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="62"/>
-      <c r="C10" s="62"/>
-      <c r="D10" s="62"/>
-      <c r="E10" s="62"/>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="62"/>
-      <c r="J10" s="62"/>
-      <c r="K10" s="62"/>
-      <c r="L10" s="62"/>
-      <c r="M10" s="62"/>
-    </row>
-    <row r="11" spans="1:13" ht="25">
-      <c r="A11" s="62" t="s">
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="57"/>
+      <c r="M10" s="57"/>
+    </row>
+    <row r="11" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A11" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="62"/>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="62" t="s">
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="62"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="59" t="s">
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="60"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="59" t="s">
+      <c r="I11" s="59"/>
+      <c r="J11" s="60"/>
+      <c r="K11" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="60"/>
-      <c r="M11" s="61"/>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="L11" s="59"/>
+      <c r="M11" s="60"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="17"/>
       <c r="B12" s="19" t="s">
         <v>51</v>
@@ -19638,7 +19629,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="19" t="s">
         <v>55</v>
       </c>
@@ -19655,47 +19646,47 @@
       <c r="L13" s="41"/>
       <c r="M13" s="41"/>
     </row>
-    <row r="14" spans="1:13" ht="25">
-      <c r="A14" s="62" t="s">
+    <row r="14" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A14" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="62"/>
-      <c r="M14" s="62"/>
-    </row>
-    <row r="15" spans="1:13" ht="25">
-      <c r="A15" s="62" t="s">
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="57"/>
+      <c r="L14" s="57"/>
+      <c r="M14" s="57"/>
+    </row>
+    <row r="15" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A15" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="62" t="s">
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="62"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="59" t="s">
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="60"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="59" t="s">
+      <c r="I15" s="59"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L15" s="60"/>
-      <c r="M15" s="61"/>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="L15" s="59"/>
+      <c r="M15" s="60"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="17"/>
       <c r="B16" s="19" t="s">
         <v>51</v>
@@ -19734,7 +19725,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="19" t="s">
         <v>55</v>
       </c>
@@ -19751,22 +19742,10 @@
         <v>0.114628122</v>
       </c>
       <c r="L17" s="11"/>
-      <c r="M17" s="11">
-        <v>1.8173954400000001E-2</v>
-      </c>
+      <c r="M17" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="K11:M11"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="K3:M3"/>
     <mergeCell ref="A2:M2"/>
@@ -19778,6 +19757,16 @@
     <mergeCell ref="E3:G3"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="K7:M7"/>
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="K15:M15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19786,99 +19775,99 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Q78"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.69140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.07421875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.69140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.07421875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.765625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="30.69140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.07421875" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.69140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.07421875" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="13.69140625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" style="10" customWidth="1"/>
+    <col min="7" max="7" width="30.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="13.6640625" style="6" customWidth="1"/>
     <col min="18" max="16384" width="11" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="25">
-      <c r="A1" s="66" t="s">
+    <row r="1" spans="1:17" ht="27" x14ac:dyDescent="0.2">
+      <c r="A1" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-    </row>
-    <row r="2" spans="1:17" ht="59.15" customHeight="1">
-      <c r="A2" s="68" t="s">
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+    </row>
+    <row r="2" spans="1:17" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="70"/>
-    </row>
-    <row r="3" spans="1:17" s="27" customFormat="1" ht="25">
-      <c r="A3" s="62" t="s">
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="69"/>
+    </row>
+    <row r="3" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A3" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-    </row>
-    <row r="4" spans="1:17" s="27" customFormat="1" ht="25">
-      <c r="A4" s="62" t="s">
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+    </row>
+    <row r="4" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A4" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62" t="s">
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62" t="s">
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="62"/>
-      <c r="L4" s="62"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
       <c r="N4" s="18"/>
       <c r="O4" s="18"/>
       <c r="P4" s="18"/>
       <c r="Q4" s="18"/>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
         <v>50</v>
       </c>
@@ -19916,7 +19905,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="19">
         <v>1</v>
       </c>
@@ -19950,7 +19939,7 @@
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D7" s="19">
         <v>2</v>
       </c>
@@ -19977,7 +19966,7 @@
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D8" s="19">
         <v>3</v>
       </c>
@@ -20004,7 +19993,7 @@
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D9" s="19"/>
       <c r="E9" s="11"/>
       <c r="F9" s="19"/>
@@ -20027,7 +20016,7 @@
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
       <c r="G10" s="19">
@@ -20049,7 +20038,7 @@
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
       <c r="G11" s="19">
@@ -20071,7 +20060,7 @@
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
       <c r="G12" s="19">
@@ -20093,7 +20082,7 @@
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
       <c r="G13" s="19"/>
@@ -20111,7 +20100,7 @@
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
       <c r="G14" s="10"/>
@@ -20129,7 +20118,7 @@
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
       <c r="G15" s="10"/>
@@ -20147,7 +20136,7 @@
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
       <c r="G16" s="10"/>
@@ -20165,7 +20154,7 @@
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
       <c r="G17" s="10"/>
@@ -20183,7 +20172,7 @@
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
       <c r="G18" s="10"/>
@@ -20201,7 +20190,7 @@
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
       <c r="G19" s="10"/>
@@ -20219,7 +20208,7 @@
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
       <c r="G20" s="10"/>
@@ -20237,7 +20226,7 @@
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
       <c r="G21" s="10"/>
@@ -20251,52 +20240,52 @@
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
     </row>
-    <row r="22" spans="1:17" s="27" customFormat="1" ht="25">
-      <c r="A22" s="67" t="s">
+    <row r="22" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A22" s="70" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="67"/>
-      <c r="C22" s="67"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="67"/>
-      <c r="J22" s="67"/>
-      <c r="K22" s="67"/>
-      <c r="L22" s="67"/>
+      <c r="B22" s="70"/>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70"/>
+      <c r="J22" s="70"/>
+      <c r="K22" s="70"/>
+      <c r="L22" s="70"/>
       <c r="M22" s="28"/>
       <c r="O22" s="29"/>
       <c r="P22" s="29"/>
       <c r="Q22" s="29"/>
     </row>
-    <row r="23" spans="1:17" s="27" customFormat="1" ht="25">
-      <c r="A23" s="62" t="s">
+    <row r="23" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A23" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="62"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62" t="s">
+      <c r="B23" s="57"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62" t="s">
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62" t="s">
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="K23" s="62"/>
-      <c r="L23" s="62"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
       <c r="O23" s="29"/>
       <c r="P23" s="29"/>
       <c r="Q23" s="29"/>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="19" t="s">
         <v>50</v>
       </c>
@@ -20337,7 +20326,7 @@
       <c r="P24" s="7"/>
       <c r="Q24" s="7"/>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="19">
         <v>1</v>
       </c>
@@ -20370,7 +20359,7 @@
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D26" s="19">
         <v>2</v>
       </c>
@@ -20396,7 +20385,7 @@
       <c r="P26" s="7"/>
       <c r="Q26" s="7"/>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D27" s="19">
         <v>3</v>
       </c>
@@ -20422,7 +20411,7 @@
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D28" s="19"/>
       <c r="E28" s="11"/>
       <c r="F28" s="19"/>
@@ -20444,7 +20433,7 @@
       <c r="P28" s="7"/>
       <c r="Q28" s="7"/>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D29" s="10"/>
       <c r="E29" s="10"/>
       <c r="G29" s="19">
@@ -20465,7 +20454,7 @@
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
     </row>
-    <row r="30" spans="1:17">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D30" s="10"/>
       <c r="E30" s="10"/>
       <c r="G30" s="19">
@@ -20486,7 +20475,7 @@
       <c r="P30" s="7"/>
       <c r="Q30" s="7"/>
     </row>
-    <row r="31" spans="1:17">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D31" s="10"/>
       <c r="E31" s="10"/>
       <c r="G31" s="19">
@@ -20507,7 +20496,7 @@
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
     </row>
-    <row r="32" spans="1:17">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
       <c r="G32" s="19"/>
@@ -20524,7 +20513,7 @@
       <c r="P32" s="7"/>
       <c r="Q32" s="7"/>
     </row>
-    <row r="33" spans="1:17">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
       <c r="G33" s="10"/>
@@ -20541,7 +20530,7 @@
       <c r="P33" s="7"/>
       <c r="Q33" s="7"/>
     </row>
-    <row r="34" spans="1:17">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
       <c r="G34" s="10"/>
@@ -20558,7 +20547,7 @@
       <c r="P34" s="7"/>
       <c r="Q34" s="7"/>
     </row>
-    <row r="35" spans="1:17">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
       <c r="G35" s="10"/>
@@ -20575,7 +20564,7 @@
       <c r="P35" s="7"/>
       <c r="Q35" s="7"/>
     </row>
-    <row r="36" spans="1:17">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
       <c r="G36" s="10"/>
@@ -20592,7 +20581,7 @@
       <c r="P36" s="7"/>
       <c r="Q36" s="7"/>
     </row>
-    <row r="37" spans="1:17">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
       <c r="G37" s="10"/>
@@ -20609,7 +20598,7 @@
       <c r="P37" s="7"/>
       <c r="Q37" s="7"/>
     </row>
-    <row r="38" spans="1:17">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
       <c r="G38" s="10"/>
@@ -20626,7 +20615,7 @@
       <c r="P38" s="7"/>
       <c r="Q38" s="7"/>
     </row>
-    <row r="39" spans="1:17">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
       <c r="G39" s="10"/>
@@ -20643,7 +20632,7 @@
       <c r="P39" s="7"/>
       <c r="Q39" s="7"/>
     </row>
-    <row r="40" spans="1:17">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D40" s="10"/>
       <c r="E40" s="10"/>
       <c r="G40" s="10"/>
@@ -20656,48 +20645,48 @@
       <c r="P40" s="7"/>
       <c r="Q40" s="7"/>
     </row>
-    <row r="41" spans="1:17" s="27" customFormat="1" ht="25">
-      <c r="A41" s="67" t="s">
+    <row r="41" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A41" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="B41" s="67"/>
-      <c r="C41" s="67"/>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
-      <c r="H41" s="67"/>
-      <c r="I41" s="67"/>
-      <c r="J41" s="67"/>
-      <c r="K41" s="67"/>
-      <c r="L41" s="67"/>
+      <c r="B41" s="70"/>
+      <c r="C41" s="70"/>
+      <c r="D41" s="70"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="70"/>
+      <c r="H41" s="70"/>
+      <c r="I41" s="70"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="70"/>
       <c r="O41" s="29"/>
       <c r="P41" s="29"/>
       <c r="Q41" s="29"/>
     </row>
-    <row r="42" spans="1:17" s="27" customFormat="1" ht="25">
-      <c r="A42" s="62" t="s">
+    <row r="42" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A42" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="62"/>
-      <c r="C42" s="62"/>
-      <c r="D42" s="62" t="s">
+      <c r="B42" s="57"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="62"/>
-      <c r="F42" s="62"/>
-      <c r="G42" s="62" t="s">
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H42" s="62"/>
-      <c r="I42" s="62"/>
-      <c r="J42" s="62" t="s">
+      <c r="H42" s="57"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="K42" s="62"/>
-      <c r="L42" s="62"/>
-    </row>
-    <row r="43" spans="1:17">
+      <c r="K42" s="57"/>
+      <c r="L42" s="57"/>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="19" t="s">
         <v>50</v>
       </c>
@@ -20735,7 +20724,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:17">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="19">
         <v>1</v>
       </c>
@@ -20765,7 +20754,7 @@
         <v>5.6689999999999996</v>
       </c>
     </row>
-    <row r="45" spans="1:17">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D45" s="19">
         <v>2</v>
       </c>
@@ -20788,7 +20777,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:17">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D46" s="19">
         <v>3</v>
       </c>
@@ -20811,7 +20800,7 @@
         <v>12.718999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:17">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D47" s="19"/>
       <c r="E47" s="11"/>
       <c r="F47" s="19"/>
@@ -20830,7 +20819,7 @@
         <v>16.966000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:17">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D48" s="10"/>
       <c r="E48" s="10"/>
       <c r="G48" s="19">
@@ -20848,7 +20837,7 @@
         <v>20.881</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D49" s="10"/>
       <c r="E49" s="10"/>
       <c r="G49" s="19">
@@ -20866,7 +20855,7 @@
         <v>24.969000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D50" s="10"/>
       <c r="E50" s="10"/>
       <c r="G50" s="19">
@@ -20884,7 +20873,7 @@
         <v>28.847999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:12">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D51" s="10"/>
       <c r="E51" s="10"/>
       <c r="G51" s="19"/>
@@ -20898,7 +20887,7 @@
         <v>33.03</v>
       </c>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D52" s="10"/>
       <c r="E52" s="10"/>
       <c r="G52" s="10"/>
@@ -20912,7 +20901,7 @@
         <v>36.945</v>
       </c>
     </row>
-    <row r="53" spans="1:12">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D53" s="10"/>
       <c r="E53" s="10"/>
       <c r="G53" s="10"/>
@@ -20926,7 +20915,7 @@
         <v>40.929000000000002</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D54" s="10"/>
       <c r="E54" s="10"/>
       <c r="G54" s="10"/>
@@ -20940,7 +20929,7 @@
         <v>44.854999999999997</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D55" s="10"/>
       <c r="E55" s="10"/>
       <c r="G55" s="10"/>
@@ -20954,7 +20943,7 @@
         <v>50.978000000000002</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D56" s="10"/>
       <c r="E56" s="10"/>
       <c r="G56" s="10"/>
@@ -20968,7 +20957,7 @@
         <v>66.174999999999997</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D57" s="10"/>
       <c r="E57" s="10"/>
       <c r="G57" s="10"/>
@@ -20982,7 +20971,7 @@
         <v>96.876000000000005</v>
       </c>
     </row>
-    <row r="58" spans="1:12">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D58" s="10"/>
       <c r="E58" s="10"/>
       <c r="G58" s="10"/>
@@ -20996,7 +20985,7 @@
         <v>149.39099999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D59" s="10"/>
       <c r="E59" s="10"/>
       <c r="G59" s="10"/>
@@ -21006,45 +20995,45 @@
       <c r="K59" s="25"/>
       <c r="L59" s="26"/>
     </row>
-    <row r="60" spans="1:12" s="27" customFormat="1" ht="25">
-      <c r="A60" s="62" t="s">
+    <row r="60" spans="1:12" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A60" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="62"/>
-      <c r="C60" s="62"/>
-      <c r="D60" s="62"/>
-      <c r="E60" s="62"/>
-      <c r="F60" s="62"/>
-      <c r="G60" s="62"/>
-      <c r="H60" s="62"/>
-      <c r="I60" s="62"/>
-      <c r="J60" s="62"/>
-      <c r="K60" s="62"/>
-      <c r="L60" s="62"/>
-    </row>
-    <row r="61" spans="1:12" s="27" customFormat="1" ht="25">
-      <c r="A61" s="62" t="s">
+      <c r="B60" s="57"/>
+      <c r="C60" s="57"/>
+      <c r="D60" s="57"/>
+      <c r="E60" s="57"/>
+      <c r="F60" s="57"/>
+      <c r="G60" s="57"/>
+      <c r="H60" s="57"/>
+      <c r="I60" s="57"/>
+      <c r="J60" s="57"/>
+      <c r="K60" s="57"/>
+      <c r="L60" s="57"/>
+    </row>
+    <row r="61" spans="1:12" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A61" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="62"/>
-      <c r="C61" s="62"/>
-      <c r="D61" s="62" t="s">
+      <c r="B61" s="57"/>
+      <c r="C61" s="57"/>
+      <c r="D61" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="62"/>
-      <c r="F61" s="62"/>
-      <c r="G61" s="62" t="s">
+      <c r="E61" s="57"/>
+      <c r="F61" s="57"/>
+      <c r="G61" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H61" s="62"/>
-      <c r="I61" s="62"/>
-      <c r="J61" s="62" t="s">
+      <c r="H61" s="57"/>
+      <c r="I61" s="57"/>
+      <c r="J61" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="K61" s="62"/>
-      <c r="L61" s="62"/>
-    </row>
-    <row r="62" spans="1:12">
+      <c r="K61" s="57"/>
+      <c r="L61" s="57"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="19" t="s">
         <v>50</v>
       </c>
@@ -21082,7 +21071,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="19">
         <v>1</v>
       </c>
@@ -21112,7 +21101,7 @@
         <v>5.6689999999999996</v>
       </c>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D64" s="19">
         <v>2</v>
       </c>
@@ -21135,7 +21124,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="4:12">
+    <row r="65" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D65" s="19">
         <v>3</v>
       </c>
@@ -21158,7 +21147,7 @@
         <v>12.718999999999999</v>
       </c>
     </row>
-    <row r="66" spans="4:12">
+    <row r="66" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D66" s="19"/>
       <c r="E66" s="11"/>
       <c r="F66" s="19"/>
@@ -21177,7 +21166,7 @@
         <v>16.966000000000001</v>
       </c>
     </row>
-    <row r="67" spans="4:12">
+    <row r="67" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D67" s="10"/>
       <c r="E67" s="10"/>
       <c r="G67" s="19">
@@ -21195,7 +21184,7 @@
         <v>20.881</v>
       </c>
     </row>
-    <row r="68" spans="4:12">
+    <row r="68" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D68" s="10"/>
       <c r="E68" s="10"/>
       <c r="G68" s="19">
@@ -21213,7 +21202,7 @@
         <v>24.969000000000001</v>
       </c>
     </row>
-    <row r="69" spans="4:12">
+    <row r="69" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D69" s="10"/>
       <c r="E69" s="10"/>
       <c r="G69" s="19">
@@ -21231,7 +21220,7 @@
         <v>28.847999999999999</v>
       </c>
     </row>
-    <row r="70" spans="4:12">
+    <row r="70" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D70" s="10"/>
       <c r="E70" s="10"/>
       <c r="G70" s="19"/>
@@ -21245,7 +21234,7 @@
         <v>33.03</v>
       </c>
     </row>
-    <row r="71" spans="4:12">
+    <row r="71" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D71" s="10"/>
       <c r="E71" s="10"/>
       <c r="G71" s="10"/>
@@ -21259,7 +21248,7 @@
         <v>36.945</v>
       </c>
     </row>
-    <row r="72" spans="4:12">
+    <row r="72" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D72" s="10"/>
       <c r="E72" s="10"/>
       <c r="G72" s="10"/>
@@ -21273,7 +21262,7 @@
         <v>40.929000000000002</v>
       </c>
     </row>
-    <row r="73" spans="4:12">
+    <row r="73" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D73" s="10"/>
       <c r="E73" s="10"/>
       <c r="G73" s="10"/>
@@ -21287,7 +21276,7 @@
         <v>44.854999999999997</v>
       </c>
     </row>
-    <row r="74" spans="4:12">
+    <row r="74" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D74" s="10"/>
       <c r="E74" s="10"/>
       <c r="G74" s="10"/>
@@ -21301,7 +21290,7 @@
         <v>50.978000000000002</v>
       </c>
     </row>
-    <row r="75" spans="4:12">
+    <row r="75" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D75" s="10"/>
       <c r="E75" s="10"/>
       <c r="G75" s="10"/>
@@ -21315,7 +21304,7 @@
         <v>66.174999999999997</v>
       </c>
     </row>
-    <row r="76" spans="4:12">
+    <row r="76" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D76" s="10"/>
       <c r="E76" s="10"/>
       <c r="G76" s="10"/>
@@ -21329,7 +21318,7 @@
         <v>96.876000000000005</v>
       </c>
     </row>
-    <row r="77" spans="4:12">
+    <row r="77" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D77" s="10"/>
       <c r="E77" s="10"/>
       <c r="G77" s="10"/>
@@ -21343,7 +21332,7 @@
         <v>149.39099999999999</v>
       </c>
     </row>
-    <row r="78" spans="4:12">
+    <row r="78" spans="4:12" x14ac:dyDescent="0.2">
       <c r="D78" s="10"/>
       <c r="E78" s="10"/>
       <c r="G78" s="10"/>
@@ -21355,12 +21344,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A41:L41"/>
-    <mergeCell ref="A60:L60"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A3:L3"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A42:C42"/>
@@ -21377,6 +21360,12 @@
     <mergeCell ref="D42:F42"/>
     <mergeCell ref="G42:I42"/>
     <mergeCell ref="J42:L42"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A60:L60"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A3:L3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -21386,82 +21375,82 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63424B91-982A-6F4D-9CA3-A2EB040E3D0E}">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.69140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.07421875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.07421875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.07421875" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" style="6" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.07421875" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.83203125" style="6" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="25" style="6" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="11" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25">
-      <c r="A1" s="56" t="s">
+    <row r="1" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A1" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="58"/>
-    </row>
-    <row r="2" spans="1:13" ht="25">
-      <c r="A2" s="62" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="63"/>
+    </row>
+    <row r="2" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A2" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-    </row>
-    <row r="3" spans="1:13" ht="25">
-      <c r="A3" s="62" t="s">
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+    </row>
+    <row r="3" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A3" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62" t="s">
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="59" t="s">
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="60"/>
-      <c r="J3" s="61"/>
-      <c r="K3" s="59" t="s">
+      <c r="I3" s="59"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="60"/>
-      <c r="M3" s="61"/>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="L3" s="59"/>
+      <c r="M3" s="60"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="17"/>
       <c r="B4" s="19" t="s">
         <v>51</v>
@@ -21500,7 +21489,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
         <v>55</v>
       </c>
@@ -21517,51 +21506,49 @@
         <v>0.11468112599999999</v>
       </c>
       <c r="L5" s="34"/>
-      <c r="M5" s="11">
-        <v>1.1565640800000001E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25">
-      <c r="A6" s="63" t="s">
+      <c r="M5" s="11"/>
+    </row>
+    <row r="6" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A6" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="65"/>
-    </row>
-    <row r="7" spans="1:13" ht="25">
-      <c r="A7" s="62" t="s">
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="66"/>
+    </row>
+    <row r="7" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A7" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="62" t="s">
+      <c r="B7" s="57"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="59" t="s">
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="60"/>
-      <c r="J7" s="61"/>
-      <c r="K7" s="59" t="s">
+      <c r="I7" s="59"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="60"/>
-      <c r="M7" s="61"/>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="L7" s="59"/>
+      <c r="M7" s="60"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
       <c r="B8" s="19" t="s">
         <v>51</v>
@@ -21600,7 +21587,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
         <v>55</v>
       </c>
@@ -21616,54 +21603,50 @@
       <c r="K9" s="11">
         <v>0.11506248599999999</v>
       </c>
-      <c r="L9" s="72">
-        <v>5.5776881999999993E-2</v>
-      </c>
-      <c r="M9" s="11">
-        <v>1.1700481800000001E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="25">
-      <c r="A10" s="62" t="s">
+      <c r="L9" s="48"/>
+      <c r="M9" s="11"/>
+    </row>
+    <row r="10" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A10" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="62"/>
-      <c r="C10" s="62"/>
-      <c r="D10" s="62"/>
-      <c r="E10" s="62"/>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="62"/>
-      <c r="J10" s="62"/>
-      <c r="K10" s="62"/>
-      <c r="L10" s="62"/>
-      <c r="M10" s="62"/>
-    </row>
-    <row r="11" spans="1:13" ht="25">
-      <c r="A11" s="62" t="s">
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="57"/>
+      <c r="M10" s="57"/>
+    </row>
+    <row r="11" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A11" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="62"/>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="62" t="s">
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="62"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="59" t="s">
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="60"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="59" t="s">
+      <c r="I11" s="59"/>
+      <c r="J11" s="60"/>
+      <c r="K11" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="60"/>
-      <c r="M11" s="61"/>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="L11" s="59"/>
+      <c r="M11" s="60"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="17"/>
       <c r="B12" s="19" t="s">
         <v>51</v>
@@ -21702,7 +21685,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="19" t="s">
         <v>55</v>
       </c>
@@ -21719,47 +21702,47 @@
       <c r="L13" s="34"/>
       <c r="M13" s="11"/>
     </row>
-    <row r="14" spans="1:13" ht="25">
-      <c r="A14" s="62" t="s">
+    <row r="14" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A14" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="62"/>
-      <c r="M14" s="62"/>
-    </row>
-    <row r="15" spans="1:13" ht="25">
-      <c r="A15" s="62" t="s">
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="57"/>
+      <c r="L14" s="57"/>
+      <c r="M14" s="57"/>
+    </row>
+    <row r="15" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A15" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="62" t="s">
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="62"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="59" t="s">
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="60"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="59" t="s">
+      <c r="I15" s="59"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L15" s="60"/>
-      <c r="M15" s="61"/>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="L15" s="59"/>
+      <c r="M15" s="60"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="17"/>
       <c r="B16" s="19" t="s">
         <v>51</v>
@@ -21798,7 +21781,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="19" t="s">
         <v>55</v>
       </c>
@@ -21817,6 +21800,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:M3"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="E15:G15"/>
     <mergeCell ref="H15:J15"/>
@@ -21832,12 +21821,6 @@
     <mergeCell ref="H11:J11"/>
     <mergeCell ref="K11:M11"/>
     <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21846,93 +21829,93 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{675AB273-2180-584F-8A66-E764000A71E7}">
   <dimension ref="A1:L78"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.07421875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.69140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.07421875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.69140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.07421875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.69140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.07421875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="25">
-      <c r="A1" s="66" t="s">
+    <row r="1" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A1" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-    </row>
-    <row r="2" spans="1:12" s="6" customFormat="1" ht="59.15" customHeight="1">
-      <c r="A2" s="68" t="s">
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+    </row>
+    <row r="2" spans="1:12" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="70"/>
-    </row>
-    <row r="3" spans="1:12" ht="25">
-      <c r="A3" s="62" t="s">
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="69"/>
+    </row>
+    <row r="3" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A3" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-    </row>
-    <row r="4" spans="1:12" ht="25">
-      <c r="A4" s="62" t="s">
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+    </row>
+    <row r="4" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A4" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62" t="s">
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62" t="s">
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="62"/>
-      <c r="L4" s="62"/>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
         <v>50</v>
       </c>
@@ -21970,7 +21953,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="19">
         <v>1</v>
       </c>
@@ -22000,7 +21983,7 @@
         <v>5.6689999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -22026,7 +22009,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -22052,7 +22035,7 @@
         <v>12.718999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -22074,7 +22057,7 @@
         <v>16.966000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -22096,7 +22079,7 @@
         <v>20.881</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -22118,7 +22101,7 @@
         <v>24.969000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -22140,7 +22123,7 @@
         <v>28.847999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -22158,7 +22141,7 @@
         <v>33.03</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -22176,7 +22159,7 @@
         <v>36.945</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -22194,7 +22177,7 @@
         <v>40.929000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -22212,7 +22195,7 @@
         <v>44.854999999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -22230,7 +22213,7 @@
         <v>50.978000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -22248,7 +22231,7 @@
         <v>66.174999999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -22266,7 +22249,7 @@
         <v>96.876000000000005</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -22284,7 +22267,7 @@
         <v>149.39099999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -22298,45 +22281,45 @@
       <c r="K21" s="25"/>
       <c r="L21" s="26"/>
     </row>
-    <row r="22" spans="1:12" ht="25">
-      <c r="A22" s="67" t="s">
+    <row r="22" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A22" s="70" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="67"/>
-      <c r="C22" s="67"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="67"/>
-      <c r="J22" s="67"/>
-      <c r="K22" s="67"/>
-      <c r="L22" s="67"/>
-    </row>
-    <row r="23" spans="1:12" ht="25">
-      <c r="A23" s="62" t="s">
+      <c r="B22" s="70"/>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70"/>
+      <c r="J22" s="70"/>
+      <c r="K22" s="70"/>
+      <c r="L22" s="70"/>
+    </row>
+    <row r="23" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A23" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="62"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62" t="s">
+      <c r="B23" s="57"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62" t="s">
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62" t="s">
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="K23" s="62"/>
-      <c r="L23" s="62"/>
-    </row>
-    <row r="24" spans="1:12">
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="19" t="s">
         <v>50</v>
       </c>
@@ -22374,7 +22357,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="19">
         <v>1</v>
       </c>
@@ -22404,7 +22387,7 @@
         <v>5.6689999999999996</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -22430,7 +22413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -22456,7 +22439,7 @@
         <v>12.718999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -22478,7 +22461,7 @@
         <v>16.966000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -22500,7 +22483,7 @@
         <v>20.881</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -22522,7 +22505,7 @@
         <v>24.969000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -22544,7 +22527,7 @@
         <v>28.847999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -22562,7 +22545,7 @@
         <v>33.03</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -22580,7 +22563,7 @@
         <v>36.945</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -22598,7 +22581,7 @@
         <v>40.929000000000002</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -22616,7 +22599,7 @@
         <v>44.854999999999997</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -22634,7 +22617,7 @@
         <v>50.978000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -22652,7 +22635,7 @@
         <v>66.174999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -22670,7 +22653,7 @@
         <v>96.876000000000005</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -22688,7 +22671,7 @@
         <v>149.39099999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="6"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -22702,45 +22685,45 @@
       <c r="K40" s="25"/>
       <c r="L40" s="26"/>
     </row>
-    <row r="41" spans="1:12" ht="25">
-      <c r="A41" s="67" t="s">
+    <row r="41" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A41" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="B41" s="67"/>
-      <c r="C41" s="67"/>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
-      <c r="H41" s="67"/>
-      <c r="I41" s="67"/>
-      <c r="J41" s="67"/>
-      <c r="K41" s="67"/>
-      <c r="L41" s="67"/>
-    </row>
-    <row r="42" spans="1:12" ht="25">
-      <c r="A42" s="62" t="s">
+      <c r="B41" s="70"/>
+      <c r="C41" s="70"/>
+      <c r="D41" s="70"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="70"/>
+      <c r="H41" s="70"/>
+      <c r="I41" s="70"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="70"/>
+    </row>
+    <row r="42" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A42" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="62"/>
-      <c r="C42" s="62"/>
-      <c r="D42" s="62" t="s">
+      <c r="B42" s="57"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="62"/>
-      <c r="F42" s="62"/>
-      <c r="G42" s="62" t="s">
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H42" s="62"/>
-      <c r="I42" s="62"/>
-      <c r="J42" s="62" t="s">
+      <c r="H42" s="57"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="K42" s="62"/>
-      <c r="L42" s="62"/>
-    </row>
-    <row r="43" spans="1:12">
+      <c r="K42" s="57"/>
+      <c r="L42" s="57"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="19" t="s">
         <v>50</v>
       </c>
@@ -22778,7 +22761,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="19">
         <v>1</v>
       </c>
@@ -22808,7 +22791,7 @@
         <v>5.6689999999999996</v>
       </c>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -22834,7 +22817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -22860,7 +22843,7 @@
         <v>12.718999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:12">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -22882,7 +22865,7 @@
         <v>16.966000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -22904,7 +22887,7 @@
         <v>20.881</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -22926,7 +22909,7 @@
         <v>24.969000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -22948,7 +22931,7 @@
         <v>28.847999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:12">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -22966,7 +22949,7 @@
         <v>33.03</v>
       </c>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -22984,7 +22967,7 @@
         <v>36.945</v>
       </c>
     </row>
-    <row r="53" spans="1:12">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -23002,7 +22985,7 @@
         <v>40.929000000000002</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -23020,7 +23003,7 @@
         <v>44.854999999999997</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -23038,7 +23021,7 @@
         <v>50.978000000000002</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -23056,7 +23039,7 @@
         <v>66.174999999999997</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -23074,7 +23057,7 @@
         <v>96.876000000000005</v>
       </c>
     </row>
-    <row r="58" spans="1:12">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -23092,7 +23075,7 @@
         <v>149.39099999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -23106,45 +23089,45 @@
       <c r="K59" s="25"/>
       <c r="L59" s="26"/>
     </row>
-    <row r="60" spans="1:12" ht="25">
-      <c r="A60" s="62" t="s">
+    <row r="60" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A60" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="62"/>
-      <c r="C60" s="62"/>
-      <c r="D60" s="62"/>
-      <c r="E60" s="62"/>
-      <c r="F60" s="62"/>
-      <c r="G60" s="62"/>
-      <c r="H60" s="62"/>
-      <c r="I60" s="62"/>
-      <c r="J60" s="62"/>
-      <c r="K60" s="62"/>
-      <c r="L60" s="62"/>
-    </row>
-    <row r="61" spans="1:12" ht="25">
-      <c r="A61" s="62" t="s">
+      <c r="B60" s="57"/>
+      <c r="C60" s="57"/>
+      <c r="D60" s="57"/>
+      <c r="E60" s="57"/>
+      <c r="F60" s="57"/>
+      <c r="G60" s="57"/>
+      <c r="H60" s="57"/>
+      <c r="I60" s="57"/>
+      <c r="J60" s="57"/>
+      <c r="K60" s="57"/>
+      <c r="L60" s="57"/>
+    </row>
+    <row r="61" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A61" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="62"/>
-      <c r="C61" s="62"/>
-      <c r="D61" s="62" t="s">
+      <c r="B61" s="57"/>
+      <c r="C61" s="57"/>
+      <c r="D61" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="62"/>
-      <c r="F61" s="62"/>
-      <c r="G61" s="62" t="s">
+      <c r="E61" s="57"/>
+      <c r="F61" s="57"/>
+      <c r="G61" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H61" s="62"/>
-      <c r="I61" s="62"/>
-      <c r="J61" s="62" t="s">
+      <c r="H61" s="57"/>
+      <c r="I61" s="57"/>
+      <c r="J61" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="K61" s="62"/>
-      <c r="L61" s="62"/>
-    </row>
-    <row r="62" spans="1:12">
+      <c r="K61" s="57"/>
+      <c r="L61" s="57"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="19" t="s">
         <v>50</v>
       </c>
@@ -23182,7 +23165,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="19">
         <v>1</v>
       </c>
@@ -23212,7 +23195,7 @@
         <v>5.6689999999999996</v>
       </c>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -23238,7 +23221,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -23264,7 +23247,7 @@
         <v>12.718999999999999</v>
       </c>
     </row>
-    <row r="66" spans="1:12">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -23286,7 +23269,7 @@
         <v>16.966000000000001</v>
       </c>
     </row>
-    <row r="67" spans="1:12">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -23308,7 +23291,7 @@
         <v>20.881</v>
       </c>
     </row>
-    <row r="68" spans="1:12">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -23330,7 +23313,7 @@
         <v>24.969000000000001</v>
       </c>
     </row>
-    <row r="69" spans="1:12">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -23352,7 +23335,7 @@
         <v>28.847999999999999</v>
       </c>
     </row>
-    <row r="70" spans="1:12">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -23370,7 +23353,7 @@
         <v>33.03</v>
       </c>
     </row>
-    <row r="71" spans="1:12">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
@@ -23388,7 +23371,7 @@
         <v>36.945</v>
       </c>
     </row>
-    <row r="72" spans="1:12">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -23406,7 +23389,7 @@
         <v>40.929000000000002</v>
       </c>
     </row>
-    <row r="73" spans="1:12">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -23424,7 +23407,7 @@
         <v>44.854999999999997</v>
       </c>
     </row>
-    <row r="74" spans="1:12">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -23442,7 +23425,7 @@
         <v>50.978000000000002</v>
       </c>
     </row>
-    <row r="75" spans="1:12">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -23460,7 +23443,7 @@
         <v>66.174999999999997</v>
       </c>
     </row>
-    <row r="76" spans="1:12">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -23478,7 +23461,7 @@
         <v>96.876000000000005</v>
       </c>
     </row>
-    <row r="77" spans="1:12">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -23496,7 +23479,7 @@
         <v>149.39099999999999</v>
       </c>
     </row>
-    <row r="78" spans="1:12">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -23512,6 +23495,13 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="A2:L2"/>
     <mergeCell ref="A61:C61"/>
     <mergeCell ref="D61:F61"/>
     <mergeCell ref="G61:I61"/>
@@ -23527,13 +23517,6 @@
     <mergeCell ref="G42:I42"/>
     <mergeCell ref="J42:L42"/>
     <mergeCell ref="A60:L60"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="A2:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23542,81 +23525,81 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A7A1387-86E1-1C48-801D-0EFBC2B89D22}">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.07421875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.07421875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.07421875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.07421875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.765625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.83203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25">
-      <c r="A1" s="56" t="s">
+    <row r="1" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A1" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="71"/>
-    </row>
-    <row r="2" spans="1:13" ht="25">
-      <c r="A2" s="59" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="72"/>
+    </row>
+    <row r="2" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A2" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="61"/>
-    </row>
-    <row r="3" spans="1:13" s="6" customFormat="1" ht="25">
-      <c r="A3" s="62" t="s">
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="60"/>
+    </row>
+    <row r="3" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A3" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62" t="s">
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="59" t="s">
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="60"/>
-      <c r="J3" s="61"/>
-      <c r="K3" s="59" t="s">
+      <c r="I3" s="59"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="60"/>
-      <c r="M3" s="61"/>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="L3" s="59"/>
+      <c r="M3" s="60"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="38"/>
       <c r="B4" s="36" t="s">
         <v>51</v>
@@ -23655,7 +23638,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="35" t="s">
         <v>55</v>
       </c>
@@ -23672,47 +23655,47 @@
       <c r="L5" s="39"/>
       <c r="M5" s="39"/>
     </row>
-    <row r="6" spans="1:13" ht="25">
-      <c r="A6" s="59" t="s">
+    <row r="6" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A6" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="60"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="61"/>
-    </row>
-    <row r="7" spans="1:13" s="6" customFormat="1" ht="25">
-      <c r="A7" s="62" t="s">
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="60"/>
+    </row>
+    <row r="7" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A7" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="62" t="s">
+      <c r="B7" s="57"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="59" t="s">
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="60"/>
-      <c r="J7" s="61"/>
-      <c r="K7" s="59" t="s">
+      <c r="I7" s="59"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="60"/>
-      <c r="M7" s="61"/>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="L7" s="59"/>
+      <c r="M7" s="60"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="38"/>
       <c r="B8" s="36" t="s">
         <v>51</v>
@@ -23751,7 +23734,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="35" t="s">
         <v>55</v>
       </c>
@@ -23768,47 +23751,47 @@
       <c r="L9" s="25"/>
       <c r="M9" s="25"/>
     </row>
-    <row r="10" spans="1:13" ht="25">
-      <c r="A10" s="59" t="s">
+    <row r="10" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A10" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="60"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="60"/>
-      <c r="K10" s="60"/>
-      <c r="L10" s="60"/>
-      <c r="M10" s="61"/>
-    </row>
-    <row r="11" spans="1:13" s="6" customFormat="1" ht="25">
-      <c r="A11" s="62" t="s">
+      <c r="B10" s="59"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="59"/>
+      <c r="K10" s="59"/>
+      <c r="L10" s="59"/>
+      <c r="M10" s="60"/>
+    </row>
+    <row r="11" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A11" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="62"/>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="62" t="s">
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="62"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="59" t="s">
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="60"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="59" t="s">
+      <c r="I11" s="59"/>
+      <c r="J11" s="60"/>
+      <c r="K11" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="60"/>
-      <c r="M11" s="61"/>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="L11" s="59"/>
+      <c r="M11" s="60"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="38"/>
       <c r="B12" s="36" t="s">
         <v>51</v>
@@ -23847,7 +23830,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="35" t="s">
         <v>55</v>
       </c>
@@ -23864,47 +23847,47 @@
       <c r="L13" s="41"/>
       <c r="M13" s="41"/>
     </row>
-    <row r="14" spans="1:13" ht="25">
-      <c r="A14" s="59" t="s">
+    <row r="14" spans="1:13" ht="27" x14ac:dyDescent="0.2">
+      <c r="A14" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="60"/>
-      <c r="K14" s="60"/>
-      <c r="L14" s="60"/>
-      <c r="M14" s="61"/>
-    </row>
-    <row r="15" spans="1:13" s="6" customFormat="1" ht="25">
-      <c r="A15" s="62" t="s">
+      <c r="B14" s="59"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="59"/>
+      <c r="J14" s="59"/>
+      <c r="K14" s="59"/>
+      <c r="L14" s="59"/>
+      <c r="M14" s="60"/>
+    </row>
+    <row r="15" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="A15" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="62" t="s">
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="62"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="59" t="s">
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="60"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="59" t="s">
+      <c r="I15" s="59"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="L15" s="60"/>
-      <c r="M15" s="61"/>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="L15" s="59"/>
+      <c r="M15" s="60"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="38"/>
       <c r="B16" s="36" t="s">
         <v>51</v>
@@ -23943,7 +23926,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="35" t="s">
         <v>55</v>
       </c>
@@ -23962,6 +23945,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:M3"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="E15:G15"/>
     <mergeCell ref="H15:J15"/>
@@ -23977,12 +23966,6 @@
     <mergeCell ref="H11:J11"/>
     <mergeCell ref="K11:M11"/>
     <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
